--- a/backend/assets/data/lg_capacities_calculated.xlsx
+++ b/backend/assets/data/lg_capacities_calculated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pardigmpartners-my.sharepoint.com/personal/alex_paradigm-esco_com/Documents/data_operations/ashp_calculator/backend/assets/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="388" documentId="11_F25DC773A252ABDACC104871611A76325ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68E5F03F-D308-4FFB-AA71-D6632484FA3D}"/>
+  <xr:revisionPtr revIDLastSave="408" documentId="11_F25DC773A252ABDACC104871611A76325ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB0C2066-5BE1-4902-8016-2C3D17C066FB}"/>
   <bookViews>
-    <workbookView xWindow="6590" yWindow="6260" windowWidth="12260" windowHeight="5370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="3260" windowWidth="30890" windowHeight="17110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="indoor_combinations" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="40">
   <si>
     <t>Indoor Capacity (kBtu/h)</t>
   </si>
@@ -137,6 +137,27 @@
   <si>
     <t>KUMXA481A</t>
   </si>
+  <si>
+    <t>KUSXA121A</t>
+  </si>
+  <si>
+    <t>KUSXA181A</t>
+  </si>
+  <si>
+    <t>KUSXA241A</t>
+  </si>
+  <si>
+    <t>KUSXA301A</t>
+  </si>
+  <si>
+    <t>KUSXA361A</t>
+  </si>
+  <si>
+    <t>KUSXA422A</t>
+  </si>
+  <si>
+    <t>KUSXA482A</t>
+  </si>
 </sst>
 </file>
 
@@ -184,13 +205,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -218,6 +245,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -483,13 +514,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4304B4-14C5-40DF-85A6-AED3FDED911B}">
-  <dimension ref="A1:X703"/>
+  <dimension ref="A1:X711"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="5.90625" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="21" max="24" width="6.81640625" bestFit="1" customWidth="1"/>
@@ -29306,6 +29339,188 @@
       </c>
       <c r="T703" s="3">
         <v>47800</v>
+      </c>
+    </row>
+    <row r="705" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A705" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B705" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C705" s="6">
+        <v>12</v>
+      </c>
+      <c r="D705" s="5">
+        <v>12</v>
+      </c>
+      <c r="E705" s="6"/>
+      <c r="F705" s="6"/>
+      <c r="G705" s="5"/>
+      <c r="H705" s="5"/>
+      <c r="I705" s="5"/>
+      <c r="J705" s="5"/>
+      <c r="L705" s="6">
+        <v>13890</v>
+      </c>
+      <c r="T705" s="6">
+        <v>13890</v>
+      </c>
+    </row>
+    <row r="706" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A706" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B706" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C706" s="6">
+        <v>18</v>
+      </c>
+      <c r="D706" s="6">
+        <v>18</v>
+      </c>
+      <c r="E706" s="6"/>
+      <c r="F706" s="6"/>
+      <c r="G706" s="5"/>
+      <c r="H706" s="5"/>
+      <c r="I706" s="5"/>
+      <c r="J706" s="5"/>
+      <c r="L706" s="6">
+        <v>22780</v>
+      </c>
+      <c r="T706" s="6">
+        <v>22780</v>
+      </c>
+    </row>
+    <row r="707" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A707" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B707" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C707" s="6">
+        <v>24</v>
+      </c>
+      <c r="D707" s="6">
+        <v>24</v>
+      </c>
+      <c r="E707" s="6"/>
+      <c r="F707" s="6"/>
+      <c r="G707" s="5"/>
+      <c r="H707" s="5"/>
+      <c r="I707" s="5"/>
+      <c r="J707" s="5"/>
+      <c r="L707" s="6">
+        <v>23330</v>
+      </c>
+      <c r="T707" s="6">
+        <v>23330</v>
+      </c>
+    </row>
+    <row r="708" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A708" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B708" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C708" s="5">
+        <v>30</v>
+      </c>
+      <c r="D708" s="5">
+        <v>30</v>
+      </c>
+      <c r="E708" s="6"/>
+      <c r="F708" s="6"/>
+      <c r="G708" s="5"/>
+      <c r="H708" s="5"/>
+      <c r="I708" s="5"/>
+      <c r="J708" s="5"/>
+      <c r="L708" s="6">
+        <v>31060</v>
+      </c>
+      <c r="T708" s="6">
+        <v>31060</v>
+      </c>
+    </row>
+    <row r="709" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A709" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B709" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C709" s="5">
+        <v>36</v>
+      </c>
+      <c r="D709" s="5">
+        <v>36</v>
+      </c>
+      <c r="E709" s="6"/>
+      <c r="F709" s="6"/>
+      <c r="G709" s="5"/>
+      <c r="H709" s="5"/>
+      <c r="I709" s="5"/>
+      <c r="J709" s="5"/>
+      <c r="L709" s="6">
+        <v>31890</v>
+      </c>
+      <c r="T709" s="6">
+        <v>31890</v>
+      </c>
+    </row>
+    <row r="710" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A710" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B710" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C710" s="5">
+        <v>42</v>
+      </c>
+      <c r="D710" s="5">
+        <v>42</v>
+      </c>
+      <c r="E710" s="6"/>
+      <c r="F710" s="6"/>
+      <c r="G710" s="5"/>
+      <c r="H710" s="5"/>
+      <c r="I710" s="5"/>
+      <c r="J710" s="5"/>
+      <c r="L710" s="6">
+        <v>42660</v>
+      </c>
+      <c r="T710" s="6">
+        <v>42660</v>
+      </c>
+    </row>
+    <row r="711" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A711" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B711" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C711" s="5">
+        <v>48</v>
+      </c>
+      <c r="D711" s="5">
+        <v>48</v>
+      </c>
+      <c r="E711" s="6"/>
+      <c r="F711" s="6"/>
+      <c r="G711" s="5"/>
+      <c r="H711" s="5"/>
+      <c r="I711" s="5"/>
+      <c r="J711" s="5"/>
+      <c r="L711" s="6">
+        <v>43220</v>
+      </c>
+      <c r="T711" s="6">
+        <v>43220</v>
       </c>
     </row>
   </sheetData>

--- a/backend/assets/data/lg_capacities_calculated.xlsx
+++ b/backend/assets/data/lg_capacities_calculated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pardigmpartners-my.sharepoint.com/personal/alex_paradigm-esco_com/Documents/data_operations/ashp_calculator/backend/assets/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="408" documentId="11_F25DC773A252ABDACC104871611A76325ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB0C2066-5BE1-4902-8016-2C3D17C066FB}"/>
+  <xr:revisionPtr revIDLastSave="419" documentId="11_F25DC773A252ABDACC104871611A76325ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68881802-D447-4311-A67D-FFFD2E9CC068}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="3260" windowWidth="30890" windowHeight="17110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3330" yWindow="620" windowWidth="30890" windowHeight="17110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="indoor_combinations" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="48">
   <si>
     <t>Indoor Capacity (kBtu/h)</t>
   </si>
@@ -158,6 +158,30 @@
   <si>
     <t>KUSXA482A</t>
   </si>
+  <si>
+    <t>Op. Watts/Htg</t>
+  </si>
+  <si>
+    <t>Breaker Req.</t>
+  </si>
+  <si>
+    <t>BTU @ 5*F</t>
+  </si>
+  <si>
+    <t>BTU @ 0*F</t>
+  </si>
+  <si>
+    <t>Tonnage</t>
+  </si>
+  <si>
+    <t>SEER2</t>
+  </si>
+  <si>
+    <t>EER2</t>
+  </si>
+  <si>
+    <t>HSPF2</t>
+  </si>
 </sst>
 </file>
 
@@ -211,13 +235,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -514,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4304B4-14C5-40DF-85A6-AED3FDED911B}">
-  <dimension ref="A1:X711"/>
+  <dimension ref="A1:AC710"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.6328125" bestFit="1" customWidth="1"/>
@@ -525,10 +549,17 @@
     <col min="7" max="11" width="5.90625" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.90625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:29" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -589,8 +620,32 @@
       <c r="T1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="V1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -617,7 +672,7 @@
         <v>16820</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -644,7 +699,7 @@
         <v>19230</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -671,7 +726,7 @@
         <v>20560</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -698,7 +753,7 @@
         <v>20560</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -725,7 +780,7 @@
         <v>20560</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -752,7 +807,7 @@
         <v>20560</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -779,7 +834,7 @@
         <v>20560</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -806,7 +861,7 @@
         <v>20560</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -836,7 +891,7 @@
         <v>15670</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -866,7 +921,7 @@
         <v>17910</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -896,7 +951,7 @@
         <v>20180</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -932,7 +987,7 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -968,7 +1023,7 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1004,7 +1059,7 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -28584,7 +28639,7 @@
         <v>47800</v>
       </c>
     </row>
-    <row r="689" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
         <v>32</v>
       </c>
@@ -28631,7 +28686,7 @@
         <v>47800</v>
       </c>
     </row>
-    <row r="690" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
         <v>32</v>
       </c>
@@ -28686,7 +28741,7 @@
         <v>47800</v>
       </c>
     </row>
-    <row r="691" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
         <v>32</v>
       </c>
@@ -28733,7 +28788,7 @@
         <v>47800</v>
       </c>
     </row>
-    <row r="692" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
         <v>32</v>
       </c>
@@ -28780,7 +28835,7 @@
         <v>47800</v>
       </c>
     </row>
-    <row r="693" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
         <v>32</v>
       </c>
@@ -28827,7 +28882,7 @@
         <v>47800</v>
       </c>
     </row>
-    <row r="694" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
         <v>32</v>
       </c>
@@ -28874,7 +28929,7 @@
         <v>47800</v>
       </c>
     </row>
-    <row r="695" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
         <v>32</v>
       </c>
@@ -28921,7 +28976,7 @@
         <v>47800</v>
       </c>
     </row>
-    <row r="696" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
         <v>32</v>
       </c>
@@ -28972,7 +29027,7 @@
         <v>47800</v>
       </c>
     </row>
-    <row r="697" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
         <v>32</v>
       </c>
@@ -29023,7 +29078,7 @@
         <v>47800</v>
       </c>
     </row>
-    <row r="698" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
         <v>32</v>
       </c>
@@ -29074,7 +29129,7 @@
         <v>47800</v>
       </c>
     </row>
-    <row r="699" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
         <v>32</v>
       </c>
@@ -29125,7 +29180,7 @@
         <v>47800</v>
       </c>
     </row>
-    <row r="700" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
         <v>32</v>
       </c>
@@ -29176,7 +29231,7 @@
         <v>47800</v>
       </c>
     </row>
-    <row r="701" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
         <v>32</v>
       </c>
@@ -29227,7 +29282,7 @@
         <v>47800</v>
       </c>
     </row>
-    <row r="702" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
         <v>32</v>
       </c>
@@ -29282,7 +29337,7 @@
         <v>47800</v>
       </c>
     </row>
-    <row r="703" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
         <v>32</v>
       </c>
@@ -29341,186 +29396,354 @@
         <v>47800</v>
       </c>
     </row>
-    <row r="705" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A705" s="5" t="s">
+    <row r="704" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A704" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B705" s="5" t="s">
+      <c r="B704" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C705" s="6">
-        <v>12</v>
+      <c r="C704" s="5">
+        <v>12</v>
+      </c>
+      <c r="D704" s="4">
+        <v>12</v>
+      </c>
+      <c r="E704" s="5"/>
+      <c r="F704" s="5"/>
+      <c r="G704" s="4"/>
+      <c r="H704" s="4"/>
+      <c r="I704" s="4"/>
+      <c r="J704" s="4"/>
+      <c r="L704" s="5">
+        <v>13890</v>
+      </c>
+      <c r="T704" s="5">
+        <v>13890</v>
+      </c>
+      <c r="V704" s="5">
+        <v>2380</v>
+      </c>
+      <c r="W704" s="4">
+        <v>30</v>
+      </c>
+      <c r="X704" s="5">
+        <v>15000</v>
+      </c>
+      <c r="Y704" s="5">
+        <v>13890</v>
+      </c>
+      <c r="Z704" s="4">
+        <v>1.04</v>
+      </c>
+      <c r="AA704" s="4">
+        <v>17</v>
+      </c>
+      <c r="AB704" s="4">
+        <v>13.3</v>
+      </c>
+      <c r="AC704" s="4">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="705" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A705" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B705" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C705" s="5">
+        <v>18</v>
       </c>
       <c r="D705" s="5">
-        <v>12</v>
-      </c>
-      <c r="E705" s="6"/>
-      <c r="F705" s="6"/>
-      <c r="G705" s="5"/>
-      <c r="H705" s="5"/>
-      <c r="I705" s="5"/>
-      <c r="J705" s="5"/>
-      <c r="L705" s="6">
-        <v>13890</v>
-      </c>
-      <c r="T705" s="6">
-        <v>13890</v>
-      </c>
-    </row>
-    <row r="706" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A706" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B706" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E705" s="5"/>
+      <c r="F705" s="5"/>
+      <c r="G705" s="4"/>
+      <c r="H705" s="4"/>
+      <c r="I705" s="4"/>
+      <c r="J705" s="4"/>
+      <c r="L705" s="5">
+        <v>22780</v>
+      </c>
+      <c r="T705" s="5">
+        <v>22780</v>
+      </c>
+      <c r="V705" s="5">
+        <v>3300</v>
+      </c>
+      <c r="W705" s="4">
+        <v>30</v>
+      </c>
+      <c r="X705" s="5">
+        <v>25000</v>
+      </c>
+      <c r="Y705" s="5">
+        <v>22780</v>
+      </c>
+      <c r="Z705" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="AA705" s="4">
+        <v>17.5</v>
+      </c>
+      <c r="AB705" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="AC705" s="4">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="706" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A706" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B706" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C706" s="6">
-        <v>18</v>
-      </c>
-      <c r="D706" s="6">
-        <v>18</v>
-      </c>
-      <c r="E706" s="6"/>
-      <c r="F706" s="6"/>
-      <c r="G706" s="5"/>
-      <c r="H706" s="5"/>
-      <c r="I706" s="5"/>
-      <c r="J706" s="5"/>
-      <c r="L706" s="6">
-        <v>22780</v>
-      </c>
-      <c r="T706" s="6">
-        <v>22780</v>
-      </c>
-    </row>
-    <row r="707" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A707" s="5" t="s">
+      <c r="C706" s="5">
+        <v>24</v>
+      </c>
+      <c r="D706" s="5">
+        <v>24</v>
+      </c>
+      <c r="E706" s="5"/>
+      <c r="F706" s="5"/>
+      <c r="G706" s="4"/>
+      <c r="H706" s="4"/>
+      <c r="I706" s="4"/>
+      <c r="J706" s="4"/>
+      <c r="L706" s="5">
+        <v>23330</v>
+      </c>
+      <c r="T706" s="5">
+        <v>23330</v>
+      </c>
+      <c r="V706" s="5">
+        <v>4584</v>
+      </c>
+      <c r="W706" s="4">
+        <v>30</v>
+      </c>
+      <c r="X706" s="5">
+        <v>25000</v>
+      </c>
+      <c r="Y706" s="5">
+        <v>23330</v>
+      </c>
+      <c r="Z706" s="4">
+        <v>2</v>
+      </c>
+      <c r="AA706" s="4">
+        <v>17.5</v>
+      </c>
+      <c r="AB706" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="AC706" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="707" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A707" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B707" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C707" s="4">
+        <v>30</v>
+      </c>
+      <c r="D707" s="4">
+        <v>30</v>
+      </c>
+      <c r="E707" s="5"/>
+      <c r="F707" s="5"/>
+      <c r="G707" s="4"/>
+      <c r="H707" s="4"/>
+      <c r="I707" s="4"/>
+      <c r="J707" s="4"/>
+      <c r="L707" s="5">
+        <v>31060</v>
+      </c>
+      <c r="T707" s="5">
+        <v>31060</v>
+      </c>
+      <c r="V707" s="4">
+        <v>7680</v>
+      </c>
+      <c r="W707" s="4">
         <v>35</v>
       </c>
-      <c r="B707" s="5" t="s">
+      <c r="X707" s="5">
+        <v>33000</v>
+      </c>
+      <c r="Y707" s="5">
+        <v>31060</v>
+      </c>
+      <c r="Z707" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="AA707" s="4">
+        <v>18.2</v>
+      </c>
+      <c r="AB707" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="AC707" s="4">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="708" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A708" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B708" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C707" s="6">
-        <v>24</v>
-      </c>
-      <c r="D707" s="6">
-        <v>24</v>
-      </c>
-      <c r="E707" s="6"/>
-      <c r="F707" s="6"/>
-      <c r="G707" s="5"/>
-      <c r="H707" s="5"/>
-      <c r="I707" s="5"/>
-      <c r="J707" s="5"/>
-      <c r="L707" s="6">
-        <v>23330</v>
-      </c>
-      <c r="T707" s="6">
-        <v>23330</v>
-      </c>
-    </row>
-    <row r="708" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A708" s="5" t="s">
+      <c r="C708" s="4">
         <v>36</v>
       </c>
-      <c r="B708" s="5" t="s">
+      <c r="D708" s="4">
+        <v>36</v>
+      </c>
+      <c r="E708" s="5"/>
+      <c r="F708" s="5"/>
+      <c r="G708" s="4"/>
+      <c r="H708" s="4"/>
+      <c r="I708" s="4"/>
+      <c r="J708" s="4"/>
+      <c r="L708" s="5">
+        <v>31890</v>
+      </c>
+      <c r="T708" s="5">
+        <v>31890</v>
+      </c>
+      <c r="V708" s="4">
+        <v>8400</v>
+      </c>
+      <c r="W708" s="4">
+        <v>35</v>
+      </c>
+      <c r="X708" s="5">
+        <v>33000</v>
+      </c>
+      <c r="Y708" s="5">
+        <v>31890</v>
+      </c>
+      <c r="Z708" s="4">
+        <v>2.75</v>
+      </c>
+      <c r="AA708" s="4">
+        <v>18.2</v>
+      </c>
+      <c r="AB708" s="4">
+        <v>13</v>
+      </c>
+      <c r="AC708" s="4">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="709" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A709" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B709" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C708" s="5">
-        <v>30</v>
-      </c>
-      <c r="D708" s="5">
-        <v>30</v>
-      </c>
-      <c r="E708" s="6"/>
-      <c r="F708" s="6"/>
-      <c r="G708" s="5"/>
-      <c r="H708" s="5"/>
-      <c r="I708" s="5"/>
-      <c r="J708" s="5"/>
-      <c r="L708" s="6">
-        <v>31060</v>
-      </c>
-      <c r="T708" s="6">
-        <v>31060</v>
-      </c>
-    </row>
-    <row r="709" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A709" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B709" s="5" t="s">
+      <c r="C709" s="4">
+        <v>42</v>
+      </c>
+      <c r="D709" s="4">
+        <v>42</v>
+      </c>
+      <c r="E709" s="5"/>
+      <c r="F709" s="5"/>
+      <c r="G709" s="4"/>
+      <c r="H709" s="4"/>
+      <c r="I709" s="4"/>
+      <c r="J709" s="4"/>
+      <c r="L709" s="5">
+        <v>42660</v>
+      </c>
+      <c r="T709" s="5">
+        <v>42660</v>
+      </c>
+      <c r="V709" s="4">
+        <v>5800</v>
+      </c>
+      <c r="W709" s="4">
+        <v>40</v>
+      </c>
+      <c r="X709" s="5">
+        <v>46000</v>
+      </c>
+      <c r="Y709" s="5">
+        <v>42660</v>
+      </c>
+      <c r="Z709" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="AA709" s="4">
+        <v>19</v>
+      </c>
+      <c r="AB709" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="AC709" s="4">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="710" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A710" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B710" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C709" s="5">
-        <v>36</v>
-      </c>
-      <c r="D709" s="5">
-        <v>36</v>
-      </c>
-      <c r="E709" s="6"/>
-      <c r="F709" s="6"/>
-      <c r="G709" s="5"/>
-      <c r="H709" s="5"/>
-      <c r="I709" s="5"/>
-      <c r="J709" s="5"/>
-      <c r="L709" s="6">
-        <v>31890</v>
-      </c>
-      <c r="T709" s="6">
-        <v>31890</v>
-      </c>
-    </row>
-    <row r="710" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A710" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B710" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C710" s="5">
-        <v>42</v>
-      </c>
-      <c r="D710" s="5">
-        <v>42</v>
-      </c>
-      <c r="E710" s="6"/>
-      <c r="F710" s="6"/>
-      <c r="G710" s="5"/>
-      <c r="H710" s="5"/>
-      <c r="I710" s="5"/>
-      <c r="J710" s="5"/>
-      <c r="L710" s="6">
-        <v>42660</v>
-      </c>
-      <c r="T710" s="6">
-        <v>42660</v>
-      </c>
-    </row>
-    <row r="711" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A711" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B711" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C711" s="5">
+      <c r="C710" s="4">
         <v>48</v>
       </c>
-      <c r="D711" s="5">
+      <c r="D710" s="4">
         <v>48</v>
       </c>
-      <c r="E711" s="6"/>
-      <c r="F711" s="6"/>
-      <c r="G711" s="5"/>
-      <c r="H711" s="5"/>
-      <c r="I711" s="5"/>
-      <c r="J711" s="5"/>
-      <c r="L711" s="6">
+      <c r="E710" s="5"/>
+      <c r="F710" s="5"/>
+      <c r="G710" s="4"/>
+      <c r="H710" s="4"/>
+      <c r="I710" s="4"/>
+      <c r="J710" s="4"/>
+      <c r="L710" s="5">
         <v>43220</v>
       </c>
-      <c r="T711" s="6">
+      <c r="T710" s="5">
         <v>43220</v>
+      </c>
+      <c r="V710" s="4">
+        <v>7680</v>
+      </c>
+      <c r="W710" s="4">
+        <v>40</v>
+      </c>
+      <c r="X710" s="5">
+        <v>46000</v>
+      </c>
+      <c r="Y710" s="5">
+        <v>43220</v>
+      </c>
+      <c r="Z710" s="4">
+        <v>3.83</v>
+      </c>
+      <c r="AA710" s="4">
+        <v>19</v>
+      </c>
+      <c r="AB710" s="4">
+        <v>12.3</v>
+      </c>
+      <c r="AC710" s="4">
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>
@@ -29541,12 +29764,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">

--- a/backend/assets/data/lg_capacities_calculated.xlsx
+++ b/backend/assets/data/lg_capacities_calculated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pardigmpartners-my.sharepoint.com/personal/alex_paradigm-esco_com/Documents/data_operations/ashp_calculator/backend/assets/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="421" documentId="11_F25DC773A252ABDACC104871611A76325ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC583F2E-ECEF-47D5-9350-B8B207F6108D}"/>
+  <xr:revisionPtr revIDLastSave="482" documentId="11_F25DC773A252ABDACC104871611A76325ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDEAC20E-C893-46CE-9F77-A228461C4B52}"/>
   <bookViews>
-    <workbookView xWindow="39540" yWindow="1970" windowWidth="30890" windowHeight="17110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1010" yWindow="180" windowWidth="17120" windowHeight="11060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="indoor_combinations" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="48">
   <si>
     <t>Model</t>
   </si>
@@ -269,10 +269,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -538,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4304B4-14C5-40DF-85A6-AED3FDED911B}">
-  <dimension ref="A1:AC710"/>
+  <dimension ref="A1:AC722"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
@@ -31852,6 +31848,426 @@
         <v>9.6</v>
       </c>
     </row>
+    <row r="711" spans="1:29" ht="29" x14ac:dyDescent="0.35">
+      <c r="A711" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B711" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C711" s="4">
+        <v>36</v>
+      </c>
+      <c r="D711" s="4">
+        <v>9</v>
+      </c>
+      <c r="E711" s="4">
+        <v>12</v>
+      </c>
+      <c r="F711" s="4">
+        <v>12</v>
+      </c>
+      <c r="L711" s="5">
+        <v>7241</v>
+      </c>
+      <c r="M711" s="5">
+        <v>9655</v>
+      </c>
+      <c r="N711" s="5">
+        <v>9655</v>
+      </c>
+      <c r="T711" s="4">
+        <v>26550</v>
+      </c>
+      <c r="Y711" s="4">
+        <v>26550</v>
+      </c>
+    </row>
+    <row r="712" spans="1:29" ht="29" x14ac:dyDescent="0.35">
+      <c r="A712" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B712" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C712" s="4">
+        <v>34</v>
+      </c>
+      <c r="D712" s="4">
+        <v>7</v>
+      </c>
+      <c r="E712" s="4">
+        <v>9</v>
+      </c>
+      <c r="F712" s="4">
+        <v>18</v>
+      </c>
+      <c r="L712" s="5">
+        <v>5466</v>
+      </c>
+      <c r="M712" s="5">
+        <v>7028</v>
+      </c>
+      <c r="N712" s="5">
+        <v>14056</v>
+      </c>
+      <c r="T712" s="4">
+        <v>26550</v>
+      </c>
+      <c r="Y712" s="4">
+        <v>26550</v>
+      </c>
+    </row>
+    <row r="713" spans="1:29" ht="29" x14ac:dyDescent="0.35">
+      <c r="A713" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B713" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C713" s="4">
+        <v>34</v>
+      </c>
+      <c r="D713" s="4">
+        <v>7</v>
+      </c>
+      <c r="E713" s="4">
+        <v>12</v>
+      </c>
+      <c r="F713" s="4">
+        <v>15</v>
+      </c>
+      <c r="L713" s="5">
+        <v>5466</v>
+      </c>
+      <c r="M713" s="5">
+        <v>9371</v>
+      </c>
+      <c r="N713" s="5">
+        <v>11713</v>
+      </c>
+      <c r="T713" s="4">
+        <v>26550</v>
+      </c>
+      <c r="Y713" s="4">
+        <v>26550</v>
+      </c>
+    </row>
+    <row r="714" spans="1:29" ht="29" x14ac:dyDescent="0.35">
+      <c r="A714" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B714" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C714" s="4">
+        <v>36</v>
+      </c>
+      <c r="D714" s="4">
+        <v>9</v>
+      </c>
+      <c r="E714" s="4">
+        <v>9</v>
+      </c>
+      <c r="F714" s="4">
+        <v>18</v>
+      </c>
+      <c r="L714" s="5">
+        <v>6638</v>
+      </c>
+      <c r="M714" s="5">
+        <v>6638</v>
+      </c>
+      <c r="N714" s="5">
+        <v>13275</v>
+      </c>
+      <c r="T714" s="4">
+        <v>26550</v>
+      </c>
+      <c r="Y714" s="4">
+        <v>26550</v>
+      </c>
+    </row>
+    <row r="715" spans="1:29" ht="29" x14ac:dyDescent="0.35">
+      <c r="A715" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B715" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C715" s="4">
+        <v>36</v>
+      </c>
+      <c r="D715" s="4">
+        <v>9</v>
+      </c>
+      <c r="E715" s="4">
+        <v>12</v>
+      </c>
+      <c r="F715" s="4">
+        <v>15</v>
+      </c>
+      <c r="L715" s="5">
+        <v>6638</v>
+      </c>
+      <c r="M715" s="5">
+        <v>8850</v>
+      </c>
+      <c r="N715" s="5">
+        <v>11063</v>
+      </c>
+      <c r="T715" s="4">
+        <v>26550</v>
+      </c>
+      <c r="Y715" s="4">
+        <v>26550</v>
+      </c>
+    </row>
+    <row r="716" spans="1:29" ht="29" x14ac:dyDescent="0.35">
+      <c r="A716" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B716" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C716" s="4">
+        <v>37</v>
+      </c>
+      <c r="D716" s="4">
+        <v>7</v>
+      </c>
+      <c r="E716" s="4">
+        <v>12</v>
+      </c>
+      <c r="F716" s="4">
+        <v>18</v>
+      </c>
+      <c r="L716" s="5">
+        <v>5023</v>
+      </c>
+      <c r="M716" s="5">
+        <v>8611</v>
+      </c>
+      <c r="N716" s="5">
+        <v>12916</v>
+      </c>
+      <c r="T716" s="4">
+        <v>26550</v>
+      </c>
+      <c r="Y716" s="4">
+        <v>26550</v>
+      </c>
+    </row>
+    <row r="717" spans="1:29" ht="29" x14ac:dyDescent="0.35">
+      <c r="A717" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B717" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C717" s="4">
+        <v>37</v>
+      </c>
+      <c r="D717" s="4">
+        <v>7</v>
+      </c>
+      <c r="E717" s="4">
+        <v>15</v>
+      </c>
+      <c r="F717" s="4">
+        <v>15</v>
+      </c>
+      <c r="L717" s="5">
+        <v>5023</v>
+      </c>
+      <c r="M717" s="5">
+        <v>10764</v>
+      </c>
+      <c r="N717" s="5">
+        <v>10764</v>
+      </c>
+      <c r="T717" s="4">
+        <v>26550</v>
+      </c>
+      <c r="Y717" s="4">
+        <v>26550</v>
+      </c>
+    </row>
+    <row r="718" spans="1:29" ht="29" x14ac:dyDescent="0.35">
+      <c r="A718" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B718" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C718" s="4">
+        <v>38</v>
+      </c>
+      <c r="D718" s="4">
+        <v>7</v>
+      </c>
+      <c r="E718" s="4">
+        <v>7</v>
+      </c>
+      <c r="F718" s="4">
+        <v>24</v>
+      </c>
+      <c r="L718" s="5">
+        <v>4891</v>
+      </c>
+      <c r="M718" s="5">
+        <v>4891</v>
+      </c>
+      <c r="N718" s="5">
+        <v>16768</v>
+      </c>
+      <c r="T718" s="4">
+        <v>26550</v>
+      </c>
+      <c r="Y718" s="4">
+        <v>26550</v>
+      </c>
+    </row>
+    <row r="719" spans="1:29" ht="29" x14ac:dyDescent="0.35">
+      <c r="A719" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B719" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C719" s="4">
+        <v>39</v>
+      </c>
+      <c r="D719" s="4">
+        <v>9</v>
+      </c>
+      <c r="E719" s="4">
+        <v>12</v>
+      </c>
+      <c r="F719" s="4">
+        <v>18</v>
+      </c>
+      <c r="L719" s="5">
+        <v>6127</v>
+      </c>
+      <c r="M719" s="5">
+        <v>8169</v>
+      </c>
+      <c r="N719" s="5">
+        <v>12254</v>
+      </c>
+      <c r="T719" s="4">
+        <v>26550</v>
+      </c>
+      <c r="Y719" s="4">
+        <v>26550</v>
+      </c>
+    </row>
+    <row r="720" spans="1:29" ht="29" x14ac:dyDescent="0.35">
+      <c r="A720" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B720" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C720" s="4">
+        <v>39</v>
+      </c>
+      <c r="D720" s="4">
+        <v>9</v>
+      </c>
+      <c r="E720" s="4">
+        <v>15</v>
+      </c>
+      <c r="F720" s="4">
+        <v>15</v>
+      </c>
+      <c r="L720" s="5">
+        <v>6127</v>
+      </c>
+      <c r="M720" s="5">
+        <v>10212</v>
+      </c>
+      <c r="N720" s="5">
+        <v>10212</v>
+      </c>
+      <c r="T720" s="4">
+        <v>26550</v>
+      </c>
+      <c r="Y720" s="4">
+        <v>26550</v>
+      </c>
+    </row>
+    <row r="721" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+      <c r="A721" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B721" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C721" s="4">
+        <v>40</v>
+      </c>
+      <c r="D721" s="4">
+        <v>7</v>
+      </c>
+      <c r="E721" s="4">
+        <v>9</v>
+      </c>
+      <c r="F721" s="4">
+        <v>24</v>
+      </c>
+      <c r="L721" s="5">
+        <v>4646</v>
+      </c>
+      <c r="M721" s="5">
+        <v>5974</v>
+      </c>
+      <c r="N721" s="5">
+        <v>15930</v>
+      </c>
+      <c r="T721" s="4">
+        <v>26550</v>
+      </c>
+      <c r="Y721" s="4">
+        <v>26550</v>
+      </c>
+    </row>
+    <row r="722" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+      <c r="A722" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B722" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C722" s="4">
+        <v>40</v>
+      </c>
+      <c r="D722" s="4">
+        <v>7</v>
+      </c>
+      <c r="E722" s="4">
+        <v>15</v>
+      </c>
+      <c r="F722" s="4">
+        <v>18</v>
+      </c>
+      <c r="L722" s="5">
+        <v>4646</v>
+      </c>
+      <c r="M722" s="5">
+        <v>9956</v>
+      </c>
+      <c r="N722" s="5">
+        <v>11948</v>
+      </c>
+      <c r="T722" s="4">
+        <v>26550</v>
+      </c>
+      <c r="Y722" s="4">
+        <v>26550</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/backend/assets/data/lg_capacities_calculated.xlsx
+++ b/backend/assets/data/lg_capacities_calculated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pardigmpartners-my.sharepoint.com/personal/alex_paradigm-esco_com/Documents/data_operations/ashp_calculator/backend/assets/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="482" documentId="11_F25DC773A252ABDACC104871611A76325ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDEAC20E-C893-46CE-9F77-A228461C4B52}"/>
+  <xr:revisionPtr revIDLastSave="483" documentId="11_F25DC773A252ABDACC104871611A76325ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{604E75D0-C17C-4B6A-A47E-B98AD20411FA}"/>
   <bookViews>
-    <workbookView xWindow="1010" yWindow="180" windowWidth="17120" windowHeight="11060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="49050" yWindow="600" windowWidth="27700" windowHeight="17110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="indoor_combinations" sheetId="2" r:id="rId1"/>
@@ -129,9 +129,6 @@
     <t>KUMXA241A</t>
   </si>
   <si>
-    <t>Non-ducted</t>
-  </si>
-  <si>
     <t>Ducted</t>
   </si>
   <si>
@@ -181,6 +178,9 @@
   </si>
   <si>
     <t>Capacity at 72F (Btu/h)</t>
+  </si>
+  <si>
+    <t>Ductless</t>
   </si>
 </sst>
 </file>
@@ -886,7 +886,7 @@
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C10">
         <v>14</v>
@@ -919,7 +919,7 @@
         <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C11">
         <v>16</v>
@@ -952,7 +952,7 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C12">
         <v>18</v>
@@ -985,7 +985,7 @@
         <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C13">
         <v>19</v>
@@ -1024,7 +1024,7 @@
         <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C14">
         <v>21</v>
@@ -1063,7 +1063,7 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C15">
         <v>22</v>
@@ -1102,7 +1102,7 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C16">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C17">
         <v>24</v>
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C18">
         <v>25</v>
@@ -1219,7 +1219,7 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C19">
         <v>27</v>
@@ -1258,7 +1258,7 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C20">
         <v>27</v>
@@ -1297,7 +1297,7 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C21">
         <v>30</v>
@@ -1336,7 +1336,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C22">
         <v>33</v>
@@ -1375,7 +1375,7 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C23">
         <v>21</v>
@@ -1418,7 +1418,7 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1461,7 +1461,7 @@
         <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C25">
         <v>25</v>
@@ -1504,7 +1504,7 @@
         <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C26">
         <v>26</v>
@@ -1547,7 +1547,7 @@
         <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C27">
         <v>27</v>
@@ -1590,7 +1590,7 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C28">
         <v>28</v>
@@ -1633,7 +1633,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C29">
         <v>29</v>
@@ -1676,7 +1676,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C30">
         <v>30</v>
@@ -1719,7 +1719,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C31">
         <v>31</v>
@@ -1762,7 +1762,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1805,7 +1805,7 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1848,7 +1848,7 @@
         <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1889,7 +1889,7 @@
         <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C35">
         <v>33</v>
@@ -1930,7 +1930,7 @@
         <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C36">
         <v>34</v>
@@ -1971,7 +1971,7 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -2012,7 +2012,7 @@
         <v>29</v>
       </c>
       <c r="B38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C38">
         <v>18</v>
@@ -2048,7 +2048,7 @@
         <v>29</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C39">
         <v>21</v>
@@ -2084,7 +2084,7 @@
         <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C40">
         <v>24</v>
@@ -2121,7 +2121,7 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C41">
         <v>27</v>
@@ -2158,7 +2158,7 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C42">
         <v>16</v>
@@ -2195,7 +2195,7 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C43">
         <v>18</v>
@@ -2232,7 +2232,7 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C44">
         <v>19</v>
@@ -2265,7 +2265,7 @@
         <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C45">
         <v>21</v>
@@ -2298,7 +2298,7 @@
         <v>29</v>
       </c>
       <c r="B46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C46">
         <v>24</v>
@@ -2331,7 +2331,7 @@
         <v>29</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C47">
         <v>24</v>
@@ -2364,7 +2364,7 @@
         <v>29</v>
       </c>
       <c r="B48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C48">
         <v>25</v>
@@ -2397,7 +2397,7 @@
         <v>29</v>
       </c>
       <c r="B49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C49">
         <v>27</v>
@@ -2430,7 +2430,7 @@
         <v>29</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C50">
         <v>27</v>
@@ -2463,7 +2463,7 @@
         <v>29</v>
       </c>
       <c r="B51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C51">
         <v>27</v>
@@ -2496,7 +2496,7 @@
         <v>29</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C52">
         <v>23</v>
@@ -2534,7 +2534,7 @@
         <v>29</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C53">
         <v>25</v>
@@ -2572,7 +2572,7 @@
         <v>29</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C54">
         <v>26</v>
@@ -2610,7 +2610,7 @@
         <v>29</v>
       </c>
       <c r="B55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C55">
         <v>28</v>
@@ -2648,7 +2648,7 @@
         <v>29</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C56">
         <v>30</v>
@@ -2686,7 +2686,7 @@
         <v>29</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C57">
         <v>32</v>
@@ -2721,10 +2721,10 @@
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C58">
         <v>18</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C59">
         <v>27</v>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C60">
         <v>16</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B61" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C61">
         <v>21</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C62">
         <v>25</v>
@@ -2871,10 +2871,10 @@
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C63">
         <v>30</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C64">
         <v>33</v>
@@ -2931,10 +2931,10 @@
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B65" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C65">
         <v>14</v>
@@ -2961,10 +2961,10 @@
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B66" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C66">
         <v>19</v>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B67" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C67">
         <v>24</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B68" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C68">
         <v>27</v>
@@ -3051,10 +3051,10 @@
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B69" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C69">
         <v>30</v>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B70" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C70">
         <v>33</v>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C71">
         <v>27</v>
@@ -3151,10 +3151,10 @@
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C72">
         <v>36</v>
@@ -3191,10 +3191,10 @@
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B73" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C73">
         <v>23</v>
@@ -3231,10 +3231,10 @@
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C74">
         <v>27</v>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C75">
         <v>31</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C76">
         <v>33</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B77" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C77">
         <v>34</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B78" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C78">
         <v>36</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B79" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C79">
         <v>21</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B80" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C80">
         <v>25</v>
@@ -3511,10 +3511,10 @@
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B81" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C81">
         <v>28</v>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B82" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C82">
         <v>31</v>
@@ -3591,10 +3591,10 @@
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B83" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C83">
         <v>33</v>
@@ -3631,10 +3631,10 @@
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B84" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C84">
         <v>34</v>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B85" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C85">
         <v>36</v>
@@ -3711,10 +3711,10 @@
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B86" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C86">
         <v>38</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B87" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C87">
         <v>39</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B88" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C88">
         <v>36</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B89" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C89">
         <v>30</v>
@@ -3883,10 +3883,10 @@
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B90" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C90">
         <v>33</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B91" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C91">
         <v>36</v>
@@ -3975,10 +3975,10 @@
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B92" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C92">
         <v>38</v>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B93" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C93">
         <v>40</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B94" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C94">
         <v>28</v>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B95" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C95">
         <v>33</v>
@@ -4159,10 +4159,10 @@
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B96" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C96">
         <v>36</v>
@@ -4205,10 +4205,10 @@
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B97" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C97">
         <v>38</v>
@@ -4251,10 +4251,10 @@
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C98">
         <v>40</v>
@@ -4297,10 +4297,10 @@
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B99" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C99">
         <v>39</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C100" s="2">
         <v>18</v>
@@ -4380,7 +4380,7 @@
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C101" s="2">
         <v>19</v>
@@ -4417,7 +4417,7 @@
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C102" s="2">
         <v>21</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C103" s="2">
         <v>21</v>
@@ -4495,7 +4495,7 @@
     </row>
     <row r="104" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C104" s="2">
         <v>22</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="105" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C105" s="2">
         <v>23</v>
@@ -4573,7 +4573,7 @@
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C106" s="2">
         <v>24</v>
@@ -4610,7 +4610,7 @@
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C107" s="2">
         <v>24</v>
@@ -4647,7 +4647,7 @@
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C108" s="2">
         <v>25</v>
@@ -4684,7 +4684,7 @@
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C109" s="2">
         <v>25</v>
@@ -4725,7 +4725,7 @@
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C110" s="2">
         <v>26</v>
@@ -4766,7 +4766,7 @@
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C111" s="2">
         <v>27</v>
@@ -4803,7 +4803,7 @@
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C112" s="2">
         <v>27</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="113" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C113" s="2">
         <v>27</v>
@@ -4881,7 +4881,7 @@
     </row>
     <row r="114" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C114" s="2">
         <v>28</v>
@@ -4922,7 +4922,7 @@
     </row>
     <row r="115" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C115" s="2">
         <v>28</v>
@@ -4967,7 +4967,7 @@
     </row>
     <row r="116" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C116" s="2">
         <v>29</v>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="117" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C117" s="2">
         <v>30</v>
@@ -5045,7 +5045,7 @@
     </row>
     <row r="118" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C118" s="2">
         <v>30</v>
@@ -5082,7 +5082,7 @@
     </row>
     <row r="119" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C119" s="2">
         <v>30</v>
@@ -5123,7 +5123,7 @@
     </row>
     <row r="120" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C120" s="2">
         <v>30</v>
@@ -5168,7 +5168,7 @@
     </row>
     <row r="121" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C121" s="2">
         <v>31</v>
@@ -5205,7 +5205,7 @@
     </row>
     <row r="122" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C122" s="2">
         <v>31</v>
@@ -5246,7 +5246,7 @@
     </row>
     <row r="123" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C123" s="2">
         <v>31</v>
@@ -5287,7 +5287,7 @@
     </row>
     <row r="124" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C124" s="2">
         <v>32</v>
@@ -5328,7 +5328,7 @@
     </row>
     <row r="125" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C125" s="2">
         <v>32</v>
@@ -5373,7 +5373,7 @@
     </row>
     <row r="126" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C126" s="2">
         <v>33</v>
@@ -5410,7 +5410,7 @@
     </row>
     <row r="127" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C127" s="2">
         <v>33</v>
@@ -5447,7 +5447,7 @@
     </row>
     <row r="128" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C128" s="2">
         <v>33</v>
@@ -5488,7 +5488,7 @@
     </row>
     <row r="129" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C129" s="2">
         <v>33</v>
@@ -5529,7 +5529,7 @@
     </row>
     <row r="130" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C130" s="2">
         <v>33</v>
@@ -5574,7 +5574,7 @@
     </row>
     <row r="131" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C131" s="2">
         <v>34</v>
@@ -5615,7 +5615,7 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C132" s="2">
         <v>34</v>
@@ -5656,7 +5656,7 @@
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C133" s="2">
         <v>34</v>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="134" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C134" s="2">
         <v>35</v>
@@ -5746,7 +5746,7 @@
     </row>
     <row r="135" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C135" s="2">
         <v>35</v>
@@ -5795,7 +5795,7 @@
     </row>
     <row r="136" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C136" s="2">
         <v>36</v>
@@ -5832,7 +5832,7 @@
     </row>
     <row r="137" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C137" s="2">
         <v>36</v>
@@ -5869,7 +5869,7 @@
     </row>
     <row r="138" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C138" s="2">
         <v>36</v>
@@ -5910,7 +5910,7 @@
     </row>
     <row r="139" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C139" s="2">
         <v>36</v>
@@ -5951,7 +5951,7 @@
     </row>
     <row r="140" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C140" s="2">
         <v>36</v>
@@ -5992,7 +5992,7 @@
     </row>
     <row r="141" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C141" s="2">
         <v>36</v>
@@ -6037,7 +6037,7 @@
     </row>
     <row r="142" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C142" s="2">
         <v>36</v>
@@ -6082,7 +6082,7 @@
     </row>
     <row r="143" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C143" s="2">
         <v>37</v>
@@ -6123,7 +6123,7 @@
     </row>
     <row r="144" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C144" s="2">
         <v>37</v>
@@ -6164,7 +6164,7 @@
     </row>
     <row r="145" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C145" s="2">
         <v>37</v>
@@ -6209,7 +6209,7 @@
     </row>
     <row r="146" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C146" s="2">
         <v>37</v>
@@ -6258,7 +6258,7 @@
     </row>
     <row r="147" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C147" s="2">
         <v>38</v>
@@ -6299,7 +6299,7 @@
     </row>
     <row r="148" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C148" s="2">
         <v>38</v>
@@ -6344,7 +6344,7 @@
     </row>
     <row r="149" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C149" s="2">
         <v>38</v>
@@ -6389,7 +6389,7 @@
     </row>
     <row r="150" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C150" s="2">
         <v>39</v>
@@ -6426,7 +6426,7 @@
     </row>
     <row r="151" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C151" s="2">
         <v>39</v>
@@ -6467,7 +6467,7 @@
     </row>
     <row r="152" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C152" s="2">
         <v>39</v>
@@ -6508,7 +6508,7 @@
     </row>
     <row r="153" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C153" s="2">
         <v>39</v>
@@ -6549,7 +6549,7 @@
     </row>
     <row r="154" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C154" s="2">
         <v>39</v>
@@ -6594,7 +6594,7 @@
     </row>
     <row r="155" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C155" s="2">
         <v>39</v>
@@ -6639,7 +6639,7 @@
     </row>
     <row r="156" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C156" s="2">
         <v>39</v>
@@ -6688,7 +6688,7 @@
     </row>
     <row r="157" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C157" s="2">
         <v>40</v>
@@ -6729,7 +6729,7 @@
     </row>
     <row r="158" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C158" s="2">
         <v>40</v>
@@ -6770,7 +6770,7 @@
     </row>
     <row r="159" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C159" s="2">
         <v>40</v>
@@ -6815,7 +6815,7 @@
     </row>
     <row r="160" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C160" s="2">
         <v>40</v>
@@ -6860,7 +6860,7 @@
     </row>
     <row r="161" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C161" s="2">
         <v>40</v>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="162" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C162" s="2">
         <v>41</v>
@@ -6954,7 +6954,7 @@
     </row>
     <row r="163" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C163" s="2">
         <v>41</v>
@@ -6999,7 +6999,7 @@
     </row>
     <row r="164" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C164" s="2">
         <v>41</v>
@@ -7048,7 +7048,7 @@
     </row>
     <row r="165" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C165" s="2">
         <v>42</v>
@@ -7085,7 +7085,7 @@
     </row>
     <row r="166" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C166" s="2">
         <v>42</v>
@@ -7126,7 +7126,7 @@
     </row>
     <row r="167" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C167" s="2">
         <v>42</v>
@@ -7167,7 +7167,7 @@
     </row>
     <row r="168" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C168" s="2">
         <v>42</v>
@@ -7208,7 +7208,7 @@
     </row>
     <row r="169" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C169" s="2">
         <v>42</v>
@@ -7249,7 +7249,7 @@
     </row>
     <row r="170" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C170" s="2">
         <v>42</v>
@@ -7294,7 +7294,7 @@
     </row>
     <row r="171" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C171" s="2">
         <v>42</v>
@@ -7338,7 +7338,7 @@
     </row>
     <row r="172" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C172" s="2">
         <v>42</v>
@@ -7386,7 +7386,7 @@
     </row>
     <row r="173" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C173" s="2">
         <v>43</v>
@@ -7426,7 +7426,7 @@
     </row>
     <row r="174" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C174" s="2">
         <v>43</v>
@@ -7466,7 +7466,7 @@
     </row>
     <row r="175" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C175" s="2">
         <v>43</v>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="176" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C176" s="2">
         <v>43</v>
@@ -7556,7 +7556,7 @@
     </row>
     <row r="177" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C177" s="2">
         <v>43</v>
@@ -7601,7 +7601,7 @@
     </row>
     <row r="178" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C178" s="2">
         <v>43</v>
@@ -7650,7 +7650,7 @@
     </row>
     <row r="179" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C179" s="2">
         <v>43</v>
@@ -7699,7 +7699,7 @@
     </row>
     <row r="180" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C180" s="2">
         <v>44</v>
@@ -7744,7 +7744,7 @@
     </row>
     <row r="181" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C181" s="2">
         <v>44</v>
@@ -7789,7 +7789,7 @@
     </row>
     <row r="182" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C182" s="2">
         <v>44</v>
@@ -7837,7 +7837,7 @@
     </row>
     <row r="183" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C183" s="2">
         <v>45</v>
@@ -7876,7 +7876,7 @@
     </row>
     <row r="184" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C184" s="2">
         <v>45</v>
@@ -7914,7 +7914,7 @@
     </row>
     <row r="185" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C185" s="2">
         <v>45</v>
@@ -7952,7 +7952,7 @@
     </row>
     <row r="186" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C186" s="2">
         <v>45</v>
@@ -7990,7 +7990,7 @@
     </row>
     <row r="187" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C187" s="2">
         <v>45</v>
@@ -8032,7 +8032,7 @@
     </row>
     <row r="188" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C188" s="2">
         <v>45</v>
@@ -8074,7 +8074,7 @@
     </row>
     <row r="189" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C189" s="2">
         <v>45</v>
@@ -8116,7 +8116,7 @@
     </row>
     <row r="190" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C190" s="2">
         <v>45</v>
@@ -8158,7 +8158,7 @@
     </row>
     <row r="191" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C191" s="2">
         <v>45</v>
@@ -8204,7 +8204,7 @@
     </row>
     <row r="192" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C192" s="2">
         <v>45</v>
@@ -8250,7 +8250,7 @@
     </row>
     <row r="193" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C193" s="2">
         <v>45</v>
@@ -8296,7 +8296,7 @@
     </row>
     <row r="194" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C194" s="2">
         <v>46</v>
@@ -8334,7 +8334,7 @@
     </row>
     <row r="195" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C195" s="2">
         <v>46</v>
@@ -8376,7 +8376,7 @@
     </row>
     <row r="196" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C196" s="2">
         <v>46</v>
@@ -8418,7 +8418,7 @@
     </row>
     <row r="197" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C197" s="2">
         <v>46</v>
@@ -8460,7 +8460,7 @@
     </row>
     <row r="198" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C198" s="2">
         <v>46</v>
@@ -8506,7 +8506,7 @@
     </row>
     <row r="199" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C199" s="2">
         <v>46</v>
@@ -8552,7 +8552,7 @@
     </row>
     <row r="200" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C200" s="2">
         <v>47</v>
@@ -8594,7 +8594,7 @@
     </row>
     <row r="201" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C201" s="2">
         <v>47</v>
@@ -8636,7 +8636,7 @@
     </row>
     <row r="202" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C202" s="2">
         <v>47</v>
@@ -8682,7 +8682,7 @@
     </row>
     <row r="203" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C203" s="2">
         <v>47</v>
@@ -8728,7 +8728,7 @@
     </row>
     <row r="204" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C204" s="2">
         <v>48</v>
@@ -8762,7 +8762,7 @@
     </row>
     <row r="205" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C205" s="2">
         <v>48</v>
@@ -8800,7 +8800,7 @@
     </row>
     <row r="206" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C206" s="2">
         <v>48</v>
@@ -8838,7 +8838,7 @@
     </row>
     <row r="207" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C207" s="2">
         <v>48</v>
@@ -8876,7 +8876,7 @@
     </row>
     <row r="208" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C208" s="2">
         <v>48</v>
@@ -8914,7 +8914,7 @@
     </row>
     <row r="209" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C209" s="2">
         <v>48</v>
@@ -8956,7 +8956,7 @@
     </row>
     <row r="210" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C210" s="2">
         <v>48</v>
@@ -8998,7 +8998,7 @@
     </row>
     <row r="211" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C211" s="2">
         <v>48</v>
@@ -9040,7 +9040,7 @@
     </row>
     <row r="212" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C212" s="2">
         <v>48</v>
@@ -9082,7 +9082,7 @@
     </row>
     <row r="213" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C213" s="2">
         <v>48</v>
@@ -9128,7 +9128,7 @@
     </row>
     <row r="214" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C214" s="2">
         <v>48</v>
@@ -9174,7 +9174,7 @@
     </row>
     <row r="215" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C215" s="2">
         <v>48</v>
@@ -9220,7 +9220,7 @@
     </row>
     <row r="216" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C216" s="2">
         <v>18</v>
@@ -9254,7 +9254,7 @@
     </row>
     <row r="217" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C217" s="2">
         <v>19</v>
@@ -9288,7 +9288,7 @@
     </row>
     <row r="218" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C218" s="2">
         <v>21</v>
@@ -9326,7 +9326,7 @@
     </row>
     <row r="219" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C219" s="2">
         <v>21</v>
@@ -9360,7 +9360,7 @@
     </row>
     <row r="220" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C220" s="2">
         <v>22</v>
@@ -9394,7 +9394,7 @@
     </row>
     <row r="221" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C221" s="2">
         <v>23</v>
@@ -9432,7 +9432,7 @@
     </row>
     <row r="222" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C222" s="2">
         <v>24</v>
@@ -9466,7 +9466,7 @@
     </row>
     <row r="223" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C223" s="2">
         <v>24</v>
@@ -9500,7 +9500,7 @@
     </row>
     <row r="224" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C224" s="2">
         <v>25</v>
@@ -9538,7 +9538,7 @@
     </row>
     <row r="225" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C225" s="2">
         <v>25</v>
@@ -9572,7 +9572,7 @@
     </row>
     <row r="226" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C226" s="2">
         <v>26</v>
@@ -9610,7 +9610,7 @@
     </row>
     <row r="227" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C227" s="2">
         <v>27</v>
@@ -9648,7 +9648,7 @@
     </row>
     <row r="228" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C228" s="2">
         <v>27</v>
@@ -9682,7 +9682,7 @@
     </row>
     <row r="229" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C229" s="2">
         <v>27</v>
@@ -9716,7 +9716,7 @@
     </row>
     <row r="230" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C230" s="2">
         <v>28</v>
@@ -9758,7 +9758,7 @@
     </row>
     <row r="231" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C231" s="2">
         <v>28</v>
@@ -9796,7 +9796,7 @@
     </row>
     <row r="232" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C232" s="2">
         <v>29</v>
@@ -9834,7 +9834,7 @@
     </row>
     <row r="233" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C233" s="2">
         <v>30</v>
@@ -9876,7 +9876,7 @@
     </row>
     <row r="234" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C234" s="2">
         <v>30</v>
@@ -9914,7 +9914,7 @@
     </row>
     <row r="235" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C235" s="2">
         <v>30</v>
@@ -9948,7 +9948,7 @@
     </row>
     <row r="236" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C236" s="2">
         <v>30</v>
@@ -9982,7 +9982,7 @@
     </row>
     <row r="237" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C237" s="2">
         <v>31</v>
@@ -10020,7 +10020,7 @@
     </row>
     <row r="238" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C238" s="2">
         <v>31</v>
@@ -10058,7 +10058,7 @@
     </row>
     <row r="239" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C239" s="2">
         <v>31</v>
@@ -10092,7 +10092,7 @@
     </row>
     <row r="240" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C240" s="2">
         <v>32</v>
@@ -10134,7 +10134,7 @@
     </row>
     <row r="241" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C241" s="2">
         <v>32</v>
@@ -10172,7 +10172,7 @@
     </row>
     <row r="242" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C242" s="2">
         <v>33</v>
@@ -10214,7 +10214,7 @@
     </row>
     <row r="243" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C243" s="2">
         <v>33</v>
@@ -10252,7 +10252,7 @@
     </row>
     <row r="244" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C244" s="2">
         <v>33</v>
@@ -10290,7 +10290,7 @@
     </row>
     <row r="245" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C245" s="2">
         <v>33</v>
@@ -10324,7 +10324,7 @@
     </row>
     <row r="246" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C246" s="2">
         <v>33</v>
@@ -10358,7 +10358,7 @@
     </row>
     <row r="247" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C247" s="2">
         <v>34</v>
@@ -10400,7 +10400,7 @@
     </row>
     <row r="248" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C248" s="2">
         <v>34</v>
@@ -10438,7 +10438,7 @@
     </row>
     <row r="249" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C249" s="2">
         <v>34</v>
@@ -10476,7 +10476,7 @@
     </row>
     <row r="250" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C250" s="2">
         <v>35</v>
@@ -10522,7 +10522,7 @@
     </row>
     <row r="251" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C251" s="2">
         <v>35</v>
@@ -10564,7 +10564,7 @@
     </row>
     <row r="252" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C252" s="2">
         <v>36</v>
@@ -10606,7 +10606,7 @@
     </row>
     <row r="253" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C253" s="2">
         <v>36</v>
@@ -10648,7 +10648,7 @@
     </row>
     <row r="254" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C254" s="2">
         <v>36</v>
@@ -10686,7 +10686,7 @@
     </row>
     <row r="255" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C255" s="2">
         <v>36</v>
@@ -10724,7 +10724,7 @@
     </row>
     <row r="256" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C256" s="2">
         <v>36</v>
@@ -10762,7 +10762,7 @@
     </row>
     <row r="257" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C257" s="2">
         <v>36</v>
@@ -10796,7 +10796,7 @@
     </row>
     <row r="258" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C258" s="2">
         <v>36</v>
@@ -10830,7 +10830,7 @@
     </row>
     <row r="259" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C259" s="2">
         <v>37</v>
@@ -10876,7 +10876,7 @@
     </row>
     <row r="260" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C260" s="2">
         <v>37</v>
@@ -10918,7 +10918,7 @@
     </row>
     <row r="261" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C261" s="2">
         <v>37</v>
@@ -10956,7 +10956,7 @@
     </row>
     <row r="262" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C262" s="2">
         <v>37</v>
@@ -10994,7 +10994,7 @@
     </row>
     <row r="263" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C263" s="2">
         <v>38</v>
@@ -11036,7 +11036,7 @@
     </row>
     <row r="264" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C264" s="2">
         <v>38</v>
@@ -11078,7 +11078,7 @@
     </row>
     <row r="265" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C265" s="2">
         <v>38</v>
@@ -11116,7 +11116,7 @@
     </row>
     <row r="266" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C266" s="2">
         <v>39</v>
@@ -11162,7 +11162,7 @@
     </row>
     <row r="267" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C267" s="2">
         <v>39</v>
@@ -11204,7 +11204,7 @@
     </row>
     <row r="268" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C268" s="2">
         <v>39</v>
@@ -11246,7 +11246,7 @@
     </row>
     <row r="269" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C269" s="2">
         <v>39</v>
@@ -11284,7 +11284,7 @@
     </row>
     <row r="270" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C270" s="2">
         <v>39</v>
@@ -11322,7 +11322,7 @@
     </row>
     <row r="271" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C271" s="2">
         <v>39</v>
@@ -11360,7 +11360,7 @@
     </row>
     <row r="272" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C272" s="2">
         <v>39</v>
@@ -11394,7 +11394,7 @@
     </row>
     <row r="273" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C273" s="2">
         <v>40</v>
@@ -11440,7 +11440,7 @@
     </row>
     <row r="274" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C274" s="2">
         <v>40</v>
@@ -11482,7 +11482,7 @@
     </row>
     <row r="275" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C275" s="2">
         <v>40</v>
@@ -11524,7 +11524,7 @@
     </row>
     <row r="276" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C276" s="2">
         <v>40</v>
@@ -11562,7 +11562,7 @@
     </row>
     <row r="277" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C277" s="2">
         <v>40</v>
@@ -11600,7 +11600,7 @@
     </row>
     <row r="278" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C278" s="2">
         <v>41</v>
@@ -11646,7 +11646,7 @@
     </row>
     <row r="279" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C279" s="2">
         <v>41</v>
@@ -11688,7 +11688,7 @@
     </row>
     <row r="280" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C280" s="2">
         <v>41</v>
@@ -11730,7 +11730,7 @@
     </row>
     <row r="281" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C281" s="2">
         <v>42</v>
@@ -11780,7 +11780,7 @@
     </row>
     <row r="282" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C282" s="2">
         <v>42</v>
@@ -11826,7 +11826,7 @@
     </row>
     <row r="283" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C283" s="2">
         <v>42</v>
@@ -11868,7 +11868,7 @@
     </row>
     <row r="284" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C284" s="2">
         <v>42</v>
@@ -11910,7 +11910,7 @@
     </row>
     <row r="285" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C285" s="2">
         <v>42</v>
@@ -11948,7 +11948,7 @@
     </row>
     <row r="286" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C286" s="2">
         <v>42</v>
@@ -11986,7 +11986,7 @@
     </row>
     <row r="287" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C287" s="2">
         <v>42</v>
@@ -12024,7 +12024,7 @@
     </row>
     <row r="288" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C288" s="2">
         <v>42</v>
@@ -12062,7 +12062,7 @@
     </row>
     <row r="289" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C289" s="2">
         <v>42</v>
@@ -12096,7 +12096,7 @@
     </row>
     <row r="290" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C290" s="2">
         <v>43</v>
@@ -12142,7 +12142,7 @@
     </row>
     <row r="291" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C291" s="2">
         <v>43</v>
@@ -12188,7 +12188,7 @@
     </row>
     <row r="292" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C292" s="2">
         <v>43</v>
@@ -12230,7 +12230,7 @@
     </row>
     <row r="293" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C293" s="2">
         <v>43</v>
@@ -12272,7 +12272,7 @@
     </row>
     <row r="294" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C294" s="2">
         <v>43</v>
@@ -12314,7 +12314,7 @@
     </row>
     <row r="295" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C295" s="2">
         <v>43</v>
@@ -12352,7 +12352,7 @@
     </row>
     <row r="296" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C296" s="2">
         <v>43</v>
@@ -12390,7 +12390,7 @@
     </row>
     <row r="297" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C297" s="2">
         <v>44</v>
@@ -12440,7 +12440,7 @@
     </row>
     <row r="298" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C298" s="2">
         <v>44</v>
@@ -12486,7 +12486,7 @@
     </row>
     <row r="299" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C299" s="2">
         <v>44</v>
@@ -12528,7 +12528,7 @@
     </row>
     <row r="300" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C300" s="2">
         <v>44</v>
@@ -12570,7 +12570,7 @@
     </row>
     <row r="301" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C301" s="2">
         <v>45</v>
@@ -12616,7 +12616,7 @@
     </row>
     <row r="302" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C302" s="2">
         <v>45</v>
@@ -12662,7 +12662,7 @@
     </row>
     <row r="303" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C303" s="2">
         <v>45</v>
@@ -12704,7 +12704,7 @@
     </row>
     <row r="304" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C304" s="2">
         <v>45</v>
@@ -12750,7 +12750,7 @@
     </row>
     <row r="305" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C305" s="2">
         <v>45</v>
@@ -12792,7 +12792,7 @@
     </row>
     <row r="306" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C306" s="2">
         <v>45</v>
@@ -12834,7 +12834,7 @@
     </row>
     <row r="307" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C307" s="2">
         <v>45</v>
@@ -12876,7 +12876,7 @@
     </row>
     <row r="308" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C308" s="2">
         <v>45</v>
@@ -12914,7 +12914,7 @@
     </row>
     <row r="309" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C309" s="2">
         <v>45</v>
@@ -12952,7 +12952,7 @@
     </row>
     <row r="310" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C310" s="2">
         <v>45</v>
@@ -12990,7 +12990,7 @@
     </row>
     <row r="311" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C311" s="2">
         <v>45</v>
@@ -13028,7 +13028,7 @@
     </row>
     <row r="312" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C312" s="2">
         <v>46</v>
@@ -13078,7 +13078,7 @@
     </row>
     <row r="313" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C313" s="2">
         <v>46</v>
@@ -13124,7 +13124,7 @@
     </row>
     <row r="314" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C314" s="2">
         <v>46</v>
@@ -13170,7 +13170,7 @@
     </row>
     <row r="315" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C315" s="2">
         <v>46</v>
@@ -13212,7 +13212,7 @@
     </row>
     <row r="316" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C316" s="2">
         <v>46</v>
@@ -13254,7 +13254,7 @@
     </row>
     <row r="317" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C317" s="2">
         <v>46</v>
@@ -13296,7 +13296,7 @@
     </row>
     <row r="318" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C318" s="2">
         <v>46</v>
@@ -13334,7 +13334,7 @@
     </row>
     <row r="319" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C319" s="2">
         <v>47</v>
@@ -13384,7 +13384,7 @@
     </row>
     <row r="320" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C320" s="2">
         <v>47</v>
@@ -13430,7 +13430,7 @@
     </row>
     <row r="321" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C321" s="2">
         <v>47</v>
@@ -13476,7 +13476,7 @@
     </row>
     <row r="322" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C322" s="2">
         <v>47</v>
@@ -13518,7 +13518,7 @@
     </row>
     <row r="323" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C323" s="2">
         <v>47</v>
@@ -13560,7 +13560,7 @@
     </row>
     <row r="324" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C324" s="2">
         <v>48</v>
@@ -13610,7 +13610,7 @@
     </row>
     <row r="325" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C325" s="2">
         <v>48</v>
@@ -13656,7 +13656,7 @@
     </row>
     <row r="326" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C326" s="2">
         <v>48</v>
@@ -13702,7 +13702,7 @@
     </row>
     <row r="327" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C327" s="2">
         <v>48</v>
@@ -13748,7 +13748,7 @@
     </row>
     <row r="328" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C328" s="2">
         <v>48</v>
@@ -13790,7 +13790,7 @@
     </row>
     <row r="329" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C329" s="2">
         <v>48</v>
@@ -13832,7 +13832,7 @@
     </row>
     <row r="330" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C330" s="2">
         <v>48</v>
@@ -13874,7 +13874,7 @@
     </row>
     <row r="331" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C331" s="2">
         <v>48</v>
@@ -13912,7 +13912,7 @@
     </row>
     <row r="332" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C332" s="2">
         <v>48</v>
@@ -13954,7 +13954,7 @@
     </row>
     <row r="333" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C333" s="2">
         <v>48</v>
@@ -13992,7 +13992,7 @@
     </row>
     <row r="334" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C334" s="2">
         <v>48</v>
@@ -14030,7 +14030,7 @@
     </row>
     <row r="335" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C335" s="2">
         <v>48</v>
@@ -14068,7 +14068,7 @@
     </row>
     <row r="336" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C336" s="2">
         <v>48</v>
@@ -14102,7 +14102,7 @@
     </row>
     <row r="337" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C337" s="2">
         <v>49</v>
@@ -14152,7 +14152,7 @@
     </row>
     <row r="338" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C338" s="2">
         <v>49</v>
@@ -14198,7 +14198,7 @@
     </row>
     <row r="339" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C339" s="2">
         <v>49</v>
@@ -14244,7 +14244,7 @@
     </row>
     <row r="340" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C340" s="2">
         <v>49</v>
@@ -14286,7 +14286,7 @@
     </row>
     <row r="341" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C341" s="2">
         <v>49</v>
@@ -14328,7 +14328,7 @@
     </row>
     <row r="342" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C342" s="2">
         <v>49</v>
@@ -14370,7 +14370,7 @@
     </row>
     <row r="343" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C343" s="2">
         <v>49</v>
@@ -14412,7 +14412,7 @@
     </row>
     <row r="344" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C344" s="2">
         <v>49</v>
@@ -14450,7 +14450,7 @@
     </row>
     <row r="345" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C345" s="2">
         <v>50</v>
@@ -14500,7 +14500,7 @@
     </row>
     <row r="346" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C346" s="2">
         <v>50</v>
@@ -14550,7 +14550,7 @@
     </row>
     <row r="347" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C347" s="2">
         <v>50</v>
@@ -14596,7 +14596,7 @@
     </row>
     <row r="348" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C348" s="2">
         <v>50</v>
@@ -14642,7 +14642,7 @@
     </row>
     <row r="349" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C349" s="2">
         <v>50</v>
@@ -14688,7 +14688,7 @@
     </row>
     <row r="350" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C350" s="2">
         <v>50</v>
@@ -14730,7 +14730,7 @@
     </row>
     <row r="351" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C351" s="2">
         <v>50</v>
@@ -14772,7 +14772,7 @@
     </row>
     <row r="352" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C352" s="2">
         <v>51</v>
@@ -14822,7 +14822,7 @@
     </row>
     <row r="353" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C353" s="2">
         <v>51</v>
@@ -14868,7 +14868,7 @@
     </row>
     <row r="354" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C354" s="2">
         <v>51</v>
@@ -14914,7 +14914,7 @@
     </row>
     <row r="355" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C355" s="2">
         <v>51</v>
@@ -14960,7 +14960,7 @@
     </row>
     <row r="356" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C356" s="2">
         <v>51</v>
@@ -15006,7 +15006,7 @@
     </row>
     <row r="357" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C357" s="2">
         <v>51</v>
@@ -15048,7 +15048,7 @@
     </row>
     <row r="358" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C358" s="2">
         <v>51</v>
@@ -15090,7 +15090,7 @@
     </row>
     <row r="359" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C359" s="2">
         <v>51</v>
@@ -15132,7 +15132,7 @@
     </row>
     <row r="360" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C360" s="2">
         <v>51</v>
@@ -15174,7 +15174,7 @@
     </row>
     <row r="361" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C361" s="2">
         <v>51</v>
@@ -15212,7 +15212,7 @@
     </row>
     <row r="362" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C362" s="2">
         <v>51</v>
@@ -15254,7 +15254,7 @@
     </row>
     <row r="363" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C363" s="2">
         <v>51</v>
@@ -15292,7 +15292,7 @@
     </row>
     <row r="364" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C364" s="2">
         <v>51</v>
@@ -15330,7 +15330,7 @@
     </row>
     <row r="365" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C365" s="2">
         <v>52</v>
@@ -15380,7 +15380,7 @@
     </row>
     <row r="366" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C366" s="2">
         <v>52</v>
@@ -15430,7 +15430,7 @@
     </row>
     <row r="367" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C367" s="2">
         <v>52</v>
@@ -15476,7 +15476,7 @@
     </row>
     <row r="368" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C368" s="2">
         <v>52</v>
@@ -15526,7 +15526,7 @@
     </row>
     <row r="369" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C369" s="2">
         <v>52</v>
@@ -15572,7 +15572,7 @@
     </row>
     <row r="370" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C370" s="2">
         <v>52</v>
@@ -15618,7 +15618,7 @@
     </row>
     <row r="371" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C371" s="2">
         <v>52</v>
@@ -15664,7 +15664,7 @@
     </row>
     <row r="372" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C372" s="2">
         <v>52</v>
@@ -15706,7 +15706,7 @@
     </row>
     <row r="373" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C373" s="2">
         <v>52</v>
@@ -15748,7 +15748,7 @@
     </row>
     <row r="374" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C374" s="2">
         <v>52</v>
@@ -15790,7 +15790,7 @@
     </row>
     <row r="375" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C375" s="2">
         <v>52</v>
@@ -15832,7 +15832,7 @@
     </row>
     <row r="376" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C376" s="2">
         <v>53</v>
@@ -15882,7 +15882,7 @@
     </row>
     <row r="377" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C377" s="2">
         <v>53</v>
@@ -15932,7 +15932,7 @@
     </row>
     <row r="378" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C378" s="2">
         <v>53</v>
@@ -15978,7 +15978,7 @@
     </row>
     <row r="379" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C379" s="2">
         <v>53</v>
@@ -16024,7 +16024,7 @@
     </row>
     <row r="380" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C380" s="2">
         <v>53</v>
@@ -16070,7 +16070,7 @@
     </row>
     <row r="381" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C381" s="2">
         <v>53</v>
@@ -16112,7 +16112,7 @@
     </row>
     <row r="382" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C382" s="2">
         <v>54</v>
@@ -16162,7 +16162,7 @@
     </row>
     <row r="383" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C383" s="2">
         <v>54</v>
@@ -16212,7 +16212,7 @@
     </row>
     <row r="384" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C384" s="2">
         <v>54</v>
@@ -16258,7 +16258,7 @@
     </row>
     <row r="385" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C385" s="2">
         <v>54</v>
@@ -16304,7 +16304,7 @@
     </row>
     <row r="386" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C386" s="2">
         <v>54</v>
@@ -16354,7 +16354,7 @@
     </row>
     <row r="387" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C387" s="2">
         <v>54</v>
@@ -16400,7 +16400,7 @@
     </row>
     <row r="388" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C388" s="2">
         <v>54</v>
@@ -16446,7 +16446,7 @@
     </row>
     <row r="389" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C389" s="2">
         <v>54</v>
@@ -16492,7 +16492,7 @@
     </row>
     <row r="390" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C390" s="2">
         <v>54</v>
@@ -16534,7 +16534,7 @@
     </row>
     <row r="391" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C391" s="2">
         <v>54</v>
@@ -16576,7 +16576,7 @@
     </row>
     <row r="392" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C392" s="2">
         <v>54</v>
@@ -16618,7 +16618,7 @@
     </row>
     <row r="393" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C393" s="2">
         <v>54</v>
@@ -16660,7 +16660,7 @@
     </row>
     <row r="394" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C394" s="2">
         <v>54</v>
@@ -16702,7 +16702,7 @@
     </row>
     <row r="395" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C395" s="2">
         <v>54</v>
@@ -16744,7 +16744,7 @@
     </row>
     <row r="396" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C396" s="2">
         <v>54</v>
@@ -16782,7 +16782,7 @@
     </row>
     <row r="397" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C397" s="2">
         <v>54</v>
@@ -16820,7 +16820,7 @@
     </row>
     <row r="398" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C398" s="2">
         <v>54</v>
@@ -16858,7 +16858,7 @@
     </row>
     <row r="399" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C399" s="2">
         <v>55</v>
@@ -16908,7 +16908,7 @@
     </row>
     <row r="400" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C400" s="2">
         <v>55</v>
@@ -16958,7 +16958,7 @@
     </row>
     <row r="401" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C401" s="2">
         <v>55</v>
@@ -17008,7 +17008,7 @@
     </row>
     <row r="402" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C402" s="2">
         <v>55</v>
@@ -17054,7 +17054,7 @@
     </row>
     <row r="403" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C403" s="2">
         <v>55</v>
@@ -17100,7 +17100,7 @@
     </row>
     <row r="404" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C404" s="2">
         <v>55</v>
@@ -17146,7 +17146,7 @@
     </row>
     <row r="405" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C405" s="2">
         <v>55</v>
@@ -17188,7 +17188,7 @@
     </row>
     <row r="406" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C406" s="2">
         <v>55</v>
@@ -17234,7 +17234,7 @@
     </row>
     <row r="407" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C407" s="2">
         <v>55</v>
@@ -17276,7 +17276,7 @@
     </row>
     <row r="408" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C408" s="2">
         <v>55</v>
@@ -17318,7 +17318,7 @@
     </row>
     <row r="409" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C409" s="2">
         <v>55</v>
@@ -17360,7 +17360,7 @@
     </row>
     <row r="410" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C410" s="2">
         <v>55</v>
@@ -17398,7 +17398,7 @@
     </row>
     <row r="411" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C411" s="2">
         <v>56</v>
@@ -17448,7 +17448,7 @@
     </row>
     <row r="412" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C412" s="2">
         <v>56</v>
@@ -17498,7 +17498,7 @@
     </row>
     <row r="413" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C413" s="2">
         <v>56</v>
@@ -17544,7 +17544,7 @@
     </row>
     <row r="414" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C414" s="2">
         <v>56</v>
@@ -17590,7 +17590,7 @@
     </row>
     <row r="415" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C415" s="2">
         <v>56</v>
@@ -17636,7 +17636,7 @@
     </row>
     <row r="416" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C416" s="2">
         <v>56</v>
@@ -17682,7 +17682,7 @@
     </row>
     <row r="417" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C417" s="2">
         <v>56</v>
@@ -17724,7 +17724,7 @@
     </row>
     <row r="418" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C418" s="2">
         <v>18</v>
@@ -17762,7 +17762,7 @@
     </row>
     <row r="419" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C419" s="2">
         <v>19</v>
@@ -17800,7 +17800,7 @@
     </row>
     <row r="420" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C420" s="2">
         <v>21</v>
@@ -17838,7 +17838,7 @@
     </row>
     <row r="421" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C421" s="2">
         <v>21</v>
@@ -17880,7 +17880,7 @@
     </row>
     <row r="422" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C422" s="2">
         <v>22</v>
@@ -17918,7 +17918,7 @@
     </row>
     <row r="423" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C423" s="2">
         <v>24</v>
@@ -17956,7 +17956,7 @@
     </row>
     <row r="424" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C424" s="2">
         <v>24</v>
@@ -17994,7 +17994,7 @@
     </row>
     <row r="425" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C425" s="2">
         <v>25</v>
@@ -18032,7 +18032,7 @@
     </row>
     <row r="426" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C426" s="2">
         <v>25</v>
@@ -18074,7 +18074,7 @@
     </row>
     <row r="427" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C427" s="2">
         <v>27</v>
@@ -18112,7 +18112,7 @@
     </row>
     <row r="428" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C428" s="2">
         <v>27</v>
@@ -18150,7 +18150,7 @@
     </row>
     <row r="429" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C429" s="2">
         <v>27</v>
@@ -18192,7 +18192,7 @@
     </row>
     <row r="430" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C430" s="2">
         <v>28</v>
@@ -18238,7 +18238,7 @@
     </row>
     <row r="431" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C431" s="2">
         <v>28</v>
@@ -18280,7 +18280,7 @@
     </row>
     <row r="432" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C432" s="2">
         <v>30</v>
@@ -18326,7 +18326,7 @@
     </row>
     <row r="433" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C433" s="2">
         <v>30</v>
@@ -18368,7 +18368,7 @@
     </row>
     <row r="434" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C434" s="2">
         <v>30</v>
@@ -18406,7 +18406,7 @@
     </row>
     <row r="435" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C435" s="2">
         <v>30</v>
@@ -18444,7 +18444,7 @@
     </row>
     <row r="436" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C436" s="2">
         <v>31</v>
@@ -18486,7 +18486,7 @@
     </row>
     <row r="437" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C437" s="2">
         <v>31</v>
@@ -18528,7 +18528,7 @@
     </row>
     <row r="438" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C438" s="2">
         <v>31</v>
@@ -18566,7 +18566,7 @@
     </row>
     <row r="439" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C439" s="2">
         <v>33</v>
@@ -18612,7 +18612,7 @@
     </row>
     <row r="440" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C440" s="2">
         <v>33</v>
@@ -18650,7 +18650,7 @@
     </row>
     <row r="441" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C441" s="2">
         <v>33</v>
@@ -18692,7 +18692,7 @@
     </row>
     <row r="442" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C442" s="2">
         <v>33</v>
@@ -18734,7 +18734,7 @@
     </row>
     <row r="443" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C443" s="2">
         <v>33</v>
@@ -18772,7 +18772,7 @@
     </row>
     <row r="444" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C444" s="2">
         <v>34</v>
@@ -18814,7 +18814,7 @@
     </row>
     <row r="445" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C445" s="2">
         <v>34</v>
@@ -18856,7 +18856,7 @@
     </row>
     <row r="446" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C446" s="2">
         <v>34</v>
@@ -18902,7 +18902,7 @@
     </row>
     <row r="447" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C447" s="2">
         <v>36</v>
@@ -18940,7 +18940,7 @@
     </row>
     <row r="448" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C448" s="2">
         <v>36</v>
@@ -18986,7 +18986,7 @@
     </row>
     <row r="449" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C449" s="2">
         <v>36</v>
@@ -19028,7 +19028,7 @@
     </row>
     <row r="450" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C450" s="2">
         <v>36</v>
@@ -19074,7 +19074,7 @@
     </row>
     <row r="451" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C451" s="2">
         <v>36</v>
@@ -19116,7 +19116,7 @@
     </row>
     <row r="452" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C452" s="2">
         <v>36</v>
@@ -19158,7 +19158,7 @@
     </row>
     <row r="453" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C453" s="2">
         <v>36</v>
@@ -19196,7 +19196,7 @@
     </row>
     <row r="454" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C454" s="2">
         <v>37</v>
@@ -19238,7 +19238,7 @@
     </row>
     <row r="455" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C455" s="2">
         <v>37</v>
@@ -19284,7 +19284,7 @@
     </row>
     <row r="456" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C456" s="2">
         <v>37</v>
@@ -19326,7 +19326,7 @@
     </row>
     <row r="457" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C457" s="2">
         <v>37</v>
@@ -19376,7 +19376,7 @@
     </row>
     <row r="458" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C458" s="2">
         <v>39</v>
@@ -19418,7 +19418,7 @@
     </row>
     <row r="459" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C459" s="2">
         <v>39</v>
@@ -19468,7 +19468,7 @@
     </row>
     <row r="460" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C460" s="2">
         <v>39</v>
@@ -19506,7 +19506,7 @@
     </row>
     <row r="461" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C461" s="2">
         <v>39</v>
@@ -19548,7 +19548,7 @@
     </row>
     <row r="462" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C462" s="2">
         <v>39</v>
@@ -19590,7 +19590,7 @@
     </row>
     <row r="463" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C463" s="2">
         <v>39</v>
@@ -19636,7 +19636,7 @@
     </row>
     <row r="464" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C464" s="2">
         <v>39</v>
@@ -19682,7 +19682,7 @@
     </row>
     <row r="465" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C465" s="2">
         <v>40</v>
@@ -19732,7 +19732,7 @@
     </row>
     <row r="466" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C466" s="2">
         <v>40</v>
@@ -19774,7 +19774,7 @@
     </row>
     <row r="467" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C467" s="2">
         <v>40</v>
@@ -19816,7 +19816,7 @@
     </row>
     <row r="468" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C468" s="2">
         <v>40</v>
@@ -19862,7 +19862,7 @@
     </row>
     <row r="469" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C469" s="2">
         <v>40</v>
@@ -19908,7 +19908,7 @@
     </row>
     <row r="470" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C470" s="2">
         <v>42</v>
@@ -19954,7 +19954,7 @@
     </row>
     <row r="471" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C471" s="2">
         <v>42</v>
@@ -19992,7 +19992,7 @@
     </row>
     <row r="472" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C472" s="2">
         <v>42</v>
@@ -20034,7 +20034,7 @@
     </row>
     <row r="473" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C473" s="2">
         <v>42</v>
@@ -20076,7 +20076,7 @@
     </row>
     <row r="474" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C474" s="2">
         <v>42</v>
@@ -20130,7 +20130,7 @@
     </row>
     <row r="475" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C475" s="2">
         <v>42</v>
@@ -20180,7 +20180,7 @@
     </row>
     <row r="476" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C476" s="2">
         <v>42</v>
@@ -20222,7 +20222,7 @@
     </row>
     <row r="477" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C477" s="2">
         <v>42</v>
@@ -20268,7 +20268,7 @@
     </row>
     <row r="478" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C478" s="2">
         <v>42</v>
@@ -20310,7 +20310,7 @@
     </row>
     <row r="479" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C479" s="2">
         <v>43</v>
@@ -20360,7 +20360,7 @@
     </row>
     <row r="480" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C480" s="2">
         <v>43</v>
@@ -20406,7 +20406,7 @@
     </row>
     <row r="481" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C481" s="2">
         <v>43</v>
@@ -20452,7 +20452,7 @@
     </row>
     <row r="482" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C482" s="2">
         <v>43</v>
@@ -20494,7 +20494,7 @@
     </row>
     <row r="483" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C483" s="2">
         <v>43</v>
@@ -20536,7 +20536,7 @@
     </row>
     <row r="484" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C484" s="2">
         <v>43</v>
@@ -20586,7 +20586,7 @@
     </row>
     <row r="485" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C485" s="2">
         <v>43</v>
@@ -20632,7 +20632,7 @@
     </row>
     <row r="486" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C486" s="2">
         <v>45</v>
@@ -20682,7 +20682,7 @@
     </row>
     <row r="487" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C487" s="2">
         <v>45</v>
@@ -20728,7 +20728,7 @@
     </row>
     <row r="488" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C488" s="2">
         <v>45</v>
@@ -20774,7 +20774,7 @@
     </row>
     <row r="489" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C489" s="2">
         <v>45</v>
@@ -20820,7 +20820,7 @@
     </row>
     <row r="490" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C490" s="2">
         <v>45</v>
@@ -20870,7 +20870,7 @@
     </row>
     <row r="491" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C491" s="2">
         <v>45</v>
@@ -20916,7 +20916,7 @@
     </row>
     <row r="492" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C492" s="2">
         <v>45</v>
@@ -20966,7 +20966,7 @@
     </row>
     <row r="493" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C493" s="2">
         <v>45</v>
@@ -21008,7 +21008,7 @@
     </row>
     <row r="494" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C494" s="2">
         <v>45</v>
@@ -21050,7 +21050,7 @@
     </row>
     <row r="495" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C495" s="2">
         <v>45</v>
@@ -21092,7 +21092,7 @@
     </row>
     <row r="496" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C496" s="2">
         <v>45</v>
@@ -21134,7 +21134,7 @@
     </row>
     <row r="497" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C497" s="2">
         <v>46</v>
@@ -21180,7 +21180,7 @@
     </row>
     <row r="498" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C498" s="2">
         <v>46</v>
@@ -21230,7 +21230,7 @@
     </row>
     <row r="499" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C499" s="2">
         <v>46</v>
@@ -21280,7 +21280,7 @@
     </row>
     <row r="500" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C500" s="2">
         <v>46</v>
@@ -21334,7 +21334,7 @@
     </row>
     <row r="501" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C501" s="2">
         <v>46</v>
@@ -21380,7 +21380,7 @@
     </row>
     <row r="502" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C502" s="2">
         <v>46</v>
@@ -21426,7 +21426,7 @@
     </row>
     <row r="503" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C503" s="2">
         <v>46</v>
@@ -21468,7 +21468,7 @@
     </row>
     <row r="504" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C504" s="2">
         <v>48</v>
@@ -21514,7 +21514,7 @@
     </row>
     <row r="505" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C505" s="2">
         <v>48</v>
@@ -21568,7 +21568,7 @@
     </row>
     <row r="506" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C506" s="2">
         <v>48</v>
@@ -21606,7 +21606,7 @@
     </row>
     <row r="507" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C507" s="2">
         <v>48</v>
@@ -21648,7 +21648,7 @@
     </row>
     <row r="508" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C508" s="2">
         <v>48</v>
@@ -21694,7 +21694,7 @@
     </row>
     <row r="509" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C509" s="2">
         <v>48</v>
@@ -21740,7 +21740,7 @@
     </row>
     <row r="510" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C510" s="2">
         <v>48</v>
@@ -21782,7 +21782,7 @@
     </row>
     <row r="511" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C511" s="2">
         <v>48</v>
@@ -21832,7 +21832,7 @@
     </row>
     <row r="512" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C512" s="2">
         <v>48</v>
@@ -21878,7 +21878,7 @@
     </row>
     <row r="513" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C513" s="2">
         <v>48</v>
@@ -21920,7 +21920,7 @@
     </row>
     <row r="514" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C514" s="2">
         <v>48</v>
@@ -21970,7 +21970,7 @@
     </row>
     <row r="515" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C515" s="2">
         <v>48</v>
@@ -22012,7 +22012,7 @@
     </row>
     <row r="516" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C516" s="2">
         <v>48</v>
@@ -22062,7 +22062,7 @@
     </row>
     <row r="517" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C517" s="2">
         <v>49</v>
@@ -22120,7 +22120,7 @@
     </row>
     <row r="518" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C518" s="2">
         <v>49</v>
@@ -22166,7 +22166,7 @@
     </row>
     <row r="519" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C519" s="2">
         <v>49</v>
@@ -22208,7 +22208,7 @@
     </row>
     <row r="520" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C520" s="2">
         <v>49</v>
@@ -22254,7 +22254,7 @@
     </row>
     <row r="521" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C521" s="2">
         <v>49</v>
@@ -22304,7 +22304,7 @@
     </row>
     <row r="522" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C522" s="2">
         <v>49</v>
@@ -22350,7 +22350,7 @@
     </row>
     <row r="523" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C523" s="2">
         <v>49</v>
@@ -22396,7 +22396,7 @@
     </row>
     <row r="524" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C524" s="2">
         <v>49</v>
@@ -22450,7 +22450,7 @@
     </row>
     <row r="525" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C525" s="2">
         <v>49</v>
@@ -22500,7 +22500,7 @@
     </row>
     <row r="526" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C526" s="2">
         <v>51</v>
@@ -22546,7 +22546,7 @@
     </row>
     <row r="527" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C527" s="2">
         <v>51</v>
@@ -22596,7 +22596,7 @@
     </row>
     <row r="528" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C528" s="2">
         <v>51</v>
@@ -22654,7 +22654,7 @@
     </row>
     <row r="529" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C529" s="2">
         <v>51</v>
@@ -22704,7 +22704,7 @@
     </row>
     <row r="530" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C530" s="2">
         <v>51</v>
@@ -22754,7 +22754,7 @@
     </row>
     <row r="531" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C531" s="2">
         <v>51</v>
@@ -22800,7 +22800,7 @@
     </row>
     <row r="532" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C532" s="2">
         <v>51</v>
@@ -22850,7 +22850,7 @@
     </row>
     <row r="533" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C533" s="2">
         <v>51</v>
@@ -22904,7 +22904,7 @@
     </row>
     <row r="534" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C534" s="2">
         <v>51</v>
@@ -22950,7 +22950,7 @@
     </row>
     <row r="535" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C535" s="2">
         <v>51</v>
@@ -22996,7 +22996,7 @@
     </row>
     <row r="536" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C536" s="2">
         <v>51</v>
@@ -23038,7 +23038,7 @@
     </row>
     <row r="537" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C537" s="2">
         <v>51</v>
@@ -23080,7 +23080,7 @@
     </row>
     <row r="538" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C538" s="2">
         <v>51</v>
@@ -23126,7 +23126,7 @@
     </row>
     <row r="539" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C539" s="2">
         <v>51</v>
@@ -23168,7 +23168,7 @@
     </row>
     <row r="540" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C540" s="2">
         <v>52</v>
@@ -23218,7 +23218,7 @@
     </row>
     <row r="541" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C541" s="2">
         <v>52</v>
@@ -23264,7 +23264,7 @@
     </row>
     <row r="542" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C542" s="2">
         <v>52</v>
@@ -23310,7 +23310,7 @@
     </row>
     <row r="543" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C543" s="2">
         <v>52</v>
@@ -23360,7 +23360,7 @@
     </row>
     <row r="544" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C544" s="2">
         <v>52</v>
@@ -23414,7 +23414,7 @@
     </row>
     <row r="545" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C545" s="2">
         <v>52</v>
@@ -23464,7 +23464,7 @@
     </row>
     <row r="546" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C546" s="2">
         <v>52</v>
@@ -23510,7 +23510,7 @@
     </row>
     <row r="547" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C547" s="2">
         <v>52</v>
@@ -23560,7 +23560,7 @@
     </row>
     <row r="548" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C548" s="2">
         <v>52</v>
@@ -23614,7 +23614,7 @@
     </row>
     <row r="549" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C549" s="2">
         <v>52</v>
@@ -23660,7 +23660,7 @@
     </row>
     <row r="550" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C550" s="2">
         <v>52</v>
@@ -23714,7 +23714,7 @@
     </row>
     <row r="551" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C551" s="2">
         <v>54</v>
@@ -23772,7 +23772,7 @@
     </row>
     <row r="552" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C552" s="2">
         <v>54</v>
@@ -23818,7 +23818,7 @@
     </row>
     <row r="553" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C553" s="2">
         <v>54</v>
@@ -23860,7 +23860,7 @@
     </row>
     <row r="554" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C554" s="2">
         <v>54</v>
@@ -23906,7 +23906,7 @@
     </row>
     <row r="555" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C555" s="2">
         <v>54</v>
@@ -23948,7 +23948,7 @@
     </row>
     <row r="556" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C556" s="2">
         <v>54</v>
@@ -23998,7 +23998,7 @@
     </row>
     <row r="557" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C557" s="2">
         <v>54</v>
@@ -24052,7 +24052,7 @@
     </row>
     <row r="558" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C558" s="2">
         <v>54</v>
@@ -24106,7 +24106,7 @@
     </row>
     <row r="559" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C559" s="2">
         <v>54</v>
@@ -24156,7 +24156,7 @@
     </row>
     <row r="560" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C560" s="2">
         <v>54</v>
@@ -24206,7 +24206,7 @@
     </row>
     <row r="561" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C561" s="2">
         <v>54</v>
@@ -24252,7 +24252,7 @@
     </row>
     <row r="562" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C562" s="2">
         <v>54</v>
@@ -24298,7 +24298,7 @@
     </row>
     <row r="563" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C563" s="2">
         <v>54</v>
@@ -24348,7 +24348,7 @@
     </row>
     <row r="564" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C564" s="2">
         <v>54</v>
@@ -24394,7 +24394,7 @@
     </row>
     <row r="565" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C565" s="2">
         <v>54</v>
@@ -24436,7 +24436,7 @@
     </row>
     <row r="566" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C566" s="2">
         <v>54</v>
@@ -24482,7 +24482,7 @@
     </row>
     <row r="567" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C567" s="2">
         <v>54</v>
@@ -24532,7 +24532,7 @@
     </row>
     <row r="568" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C568" s="2">
         <v>54</v>
@@ -24586,7 +24586,7 @@
     </row>
     <row r="569" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C569" s="2">
         <v>55</v>
@@ -24636,7 +24636,7 @@
     </row>
     <row r="570" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C570" s="2">
         <v>55</v>
@@ -24682,7 +24682,7 @@
     </row>
     <row r="571" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C571" s="2">
         <v>55</v>
@@ -24728,7 +24728,7 @@
     </row>
     <row r="572" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C572" s="2">
         <v>55</v>
@@ -24774,7 +24774,7 @@
     </row>
     <row r="573" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C573" s="2">
         <v>55</v>
@@ -24828,7 +24828,7 @@
     </row>
     <row r="574" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C574" s="2">
         <v>55</v>
@@ -24874,7 +24874,7 @@
     </row>
     <row r="575" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C575" s="2">
         <v>55</v>
@@ -24928,7 +24928,7 @@
     </row>
     <row r="576" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C576" s="2">
         <v>55</v>
@@ -24978,7 +24978,7 @@
     </row>
     <row r="577" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C577" s="2">
         <v>55</v>
@@ -25020,7 +25020,7 @@
     </row>
     <row r="578" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C578" s="2">
         <v>55</v>
@@ -25070,7 +25070,7 @@
     </row>
     <row r="579" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C579" s="2">
         <v>55</v>
@@ -25128,7 +25128,7 @@
     </row>
     <row r="580" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C580" s="2">
         <v>55</v>
@@ -25182,7 +25182,7 @@
     </row>
     <row r="581" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C581" s="2">
         <v>55</v>
@@ -25232,7 +25232,7 @@
     </row>
     <row r="582" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C582" s="2">
         <v>57</v>
@@ -25282,7 +25282,7 @@
     </row>
     <row r="583" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C583" s="2">
         <v>57</v>
@@ -25324,7 +25324,7 @@
     </row>
     <row r="584" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C584" s="2">
         <v>57</v>
@@ -25374,7 +25374,7 @@
     </row>
     <row r="585" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C585" s="2">
         <v>57</v>
@@ -25424,7 +25424,7 @@
     </row>
     <row r="586" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C586" s="2">
         <v>57</v>
@@ -25482,7 +25482,7 @@
     </row>
     <row r="587" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C587" s="2">
         <v>57</v>
@@ -25532,7 +25532,7 @@
     </row>
     <row r="588" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C588" s="2">
         <v>57</v>
@@ -25578,7 +25578,7 @@
     </row>
     <row r="589" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C589" s="2">
         <v>57</v>
@@ -25624,7 +25624,7 @@
     </row>
     <row r="590" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C590" s="2">
         <v>57</v>
@@ -25670,7 +25670,7 @@
     </row>
     <row r="591" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C591" s="2">
         <v>57</v>
@@ -25716,7 +25716,7 @@
     </row>
     <row r="592" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C592" s="2">
         <v>57</v>
@@ -25770,7 +25770,7 @@
     </row>
     <row r="593" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C593" s="2">
         <v>57</v>
@@ -25824,7 +25824,7 @@
     </row>
     <row r="594" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C594" s="2">
         <v>57</v>
@@ -25874,7 +25874,7 @@
     </row>
     <row r="595" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C595" s="2">
         <v>57</v>
@@ -25928,7 +25928,7 @@
     </row>
     <row r="596" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C596" s="2">
         <v>57</v>
@@ -25974,7 +25974,7 @@
     </row>
     <row r="597" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C597" s="2">
         <v>57</v>
@@ -26028,7 +26028,7 @@
     </row>
     <row r="598" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C598" s="2">
         <v>57</v>
@@ -26086,7 +26086,7 @@
     </row>
     <row r="599" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C599" s="2">
         <v>57</v>
@@ -26128,7 +26128,7 @@
     </row>
     <row r="600" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C600" s="2">
         <v>57</v>
@@ -26178,7 +26178,7 @@
     </row>
     <row r="601" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C601" s="2">
         <v>57</v>
@@ -26224,7 +26224,7 @@
     </row>
     <row r="602" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C602" s="2">
         <v>58</v>
@@ -26278,7 +26278,7 @@
     </row>
     <row r="603" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C603" s="2">
         <v>58</v>
@@ -26332,7 +26332,7 @@
     </row>
     <row r="604" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C604" s="2">
         <v>58</v>
@@ -26386,7 +26386,7 @@
     </row>
     <row r="605" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C605" s="2">
         <v>58</v>
@@ -26436,7 +26436,7 @@
     </row>
     <row r="606" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C606" s="2">
         <v>58</v>
@@ -26490,7 +26490,7 @@
     </row>
     <row r="607" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C607" s="2">
         <v>58</v>
@@ -26536,7 +26536,7 @@
     </row>
     <row r="608" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C608" s="2">
         <v>58</v>
@@ -26582,7 +26582,7 @@
     </row>
     <row r="609" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C609" s="2">
         <v>58</v>
@@ -26628,7 +26628,7 @@
     </row>
     <row r="610" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C610" s="2">
         <v>58</v>
@@ -26678,7 +26678,7 @@
     </row>
     <row r="611" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C611" s="2">
         <v>58</v>
@@ -26740,7 +26740,7 @@
     </row>
     <row r="612" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C612" s="2">
         <v>58</v>
@@ -26790,7 +26790,7 @@
     </row>
     <row r="613" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C613" s="2">
         <v>58</v>
@@ -26840,7 +26840,7 @@
     </row>
     <row r="614" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C614" s="2">
         <v>58</v>
@@ -26890,7 +26890,7 @@
     </row>
     <row r="615" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C615" s="2">
         <v>58</v>
@@ -26948,7 +26948,7 @@
     </row>
     <row r="616" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C616" s="2">
         <v>60</v>
@@ -26994,7 +26994,7 @@
     </row>
     <row r="617" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C617" s="2">
         <v>60</v>
@@ -27048,7 +27048,7 @@
     </row>
     <row r="618" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C618" s="2">
         <v>60</v>
@@ -27094,7 +27094,7 @@
     </row>
     <row r="619" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C619" s="2">
         <v>60</v>
@@ -27140,7 +27140,7 @@
     </row>
     <row r="620" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C620" s="2">
         <v>60</v>
@@ -27190,7 +27190,7 @@
     </row>
     <row r="621" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C621" s="2">
         <v>60</v>
@@ -27236,7 +27236,7 @@
     </row>
     <row r="622" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C622" s="2">
         <v>60</v>
@@ -27294,7 +27294,7 @@
     </row>
     <row r="623" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C623" s="2">
         <v>60</v>
@@ -27340,7 +27340,7 @@
     </row>
     <row r="624" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C624" s="2">
         <v>60</v>
@@ -27394,7 +27394,7 @@
     </row>
     <row r="625" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C625" s="2">
         <v>60</v>
@@ -27448,7 +27448,7 @@
     </row>
     <row r="626" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C626" s="2">
         <v>60</v>
@@ -27494,7 +27494,7 @@
     </row>
     <row r="627" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C627" s="2">
         <v>60</v>
@@ -27544,7 +27544,7 @@
     </row>
     <row r="628" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C628" s="2">
         <v>60</v>
@@ -27598,7 +27598,7 @@
     </row>
     <row r="629" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C629" s="2">
         <v>60</v>
@@ -27652,7 +27652,7 @@
     </row>
     <row r="630" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C630" s="2">
         <v>60</v>
@@ -27698,7 +27698,7 @@
     </row>
     <row r="631" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C631" s="2">
         <v>60</v>
@@ -27756,7 +27756,7 @@
     </row>
     <row r="632" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C632" s="2">
         <v>60</v>
@@ -27806,7 +27806,7 @@
     </row>
     <row r="633" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C633" s="2">
         <v>60</v>
@@ -27848,7 +27848,7 @@
     </row>
     <row r="634" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C634" s="2">
         <v>60</v>
@@ -27898,7 +27898,7 @@
     </row>
     <row r="635" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C635" s="2">
         <v>60</v>
@@ -27960,7 +27960,7 @@
     </row>
     <row r="636" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C636" s="2">
         <v>60</v>
@@ -28010,7 +28010,7 @@
     </row>
     <row r="637" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C637" s="2">
         <v>60</v>
@@ -28060,7 +28060,7 @@
     </row>
     <row r="638" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C638" s="2">
         <v>60</v>
@@ -28110,7 +28110,7 @@
     </row>
     <row r="639" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C639" s="2">
         <v>60</v>
@@ -28152,7 +28152,7 @@
     </row>
     <row r="640" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C640" s="2">
         <v>61</v>
@@ -28210,7 +28210,7 @@
     </row>
     <row r="641" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C641" s="2">
         <v>61</v>
@@ -28256,7 +28256,7 @@
     </row>
     <row r="642" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C642" s="2">
         <v>61</v>
@@ -28310,7 +28310,7 @@
     </row>
     <row r="643" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C643" s="2">
         <v>61</v>
@@ -28360,7 +28360,7 @@
     </row>
     <row r="644" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C644" s="2">
         <v>61</v>
@@ -28418,7 +28418,7 @@
     </row>
     <row r="645" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C645" s="2">
         <v>61</v>
@@ -28468,7 +28468,7 @@
     </row>
     <row r="646" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C646" s="2">
         <v>61</v>
@@ -28522,7 +28522,7 @@
     </row>
     <row r="647" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C647" s="2">
         <v>61</v>
@@ -28576,7 +28576,7 @@
     </row>
     <row r="648" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C648" s="2">
         <v>61</v>
@@ -28626,7 +28626,7 @@
     </row>
     <row r="649" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C649" s="2">
         <v>61</v>
@@ -28676,7 +28676,7 @@
     </row>
     <row r="650" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C650" s="2">
         <v>61</v>
@@ -28726,7 +28726,7 @@
     </row>
     <row r="651" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C651" s="2">
         <v>61</v>
@@ -28780,7 +28780,7 @@
     </row>
     <row r="652" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C652" s="2">
         <v>61</v>
@@ -28826,7 +28826,7 @@
     </row>
     <row r="653" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C653" s="2">
         <v>61</v>
@@ -28880,7 +28880,7 @@
     </row>
     <row r="654" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C654" s="2">
         <v>61</v>
@@ -28926,7 +28926,7 @@
     </row>
     <row r="655" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C655" s="2">
         <v>61</v>
@@ -28988,7 +28988,7 @@
     </row>
     <row r="656" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C656" s="2">
         <v>61</v>
@@ -29038,7 +29038,7 @@
     </row>
     <row r="657" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C657" s="2">
         <v>61</v>
@@ -29096,7 +29096,7 @@
     </row>
     <row r="658" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C658" s="2">
         <v>63</v>
@@ -29154,7 +29154,7 @@
     </row>
     <row r="659" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C659" s="2">
         <v>63</v>
@@ -29208,7 +29208,7 @@
     </row>
     <row r="660" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C660" s="2">
         <v>63</v>
@@ -29266,7 +29266,7 @@
     </row>
     <row r="661" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C661" s="2">
         <v>63</v>
@@ -29320,7 +29320,7 @@
     </row>
     <row r="662" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C662" s="2">
         <v>63</v>
@@ -29378,7 +29378,7 @@
     </row>
     <row r="663" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C663" s="2">
         <v>63</v>
@@ -29432,7 +29432,7 @@
     </row>
     <row r="664" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C664" s="2">
         <v>63</v>
@@ -29478,7 +29478,7 @@
     </row>
     <row r="665" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C665" s="2">
         <v>63</v>
@@ -29532,7 +29532,7 @@
     </row>
     <row r="666" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C666" s="2">
         <v>63</v>
@@ -29578,7 +29578,7 @@
     </row>
     <row r="667" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C667" s="2">
         <v>63</v>
@@ -29640,7 +29640,7 @@
     </row>
     <row r="668" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C668" s="2">
         <v>63</v>
@@ -29694,7 +29694,7 @@
     </row>
     <row r="669" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C669" s="2">
         <v>63</v>
@@ -29740,7 +29740,7 @@
     </row>
     <row r="670" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C670" s="2">
         <v>63</v>
@@ -29786,7 +29786,7 @@
     </row>
     <row r="671" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C671" s="2">
         <v>63</v>
@@ -29832,7 +29832,7 @@
     </row>
     <row r="672" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C672" s="2">
         <v>63</v>
@@ -29882,7 +29882,7 @@
     </row>
     <row r="673" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C673" s="2">
         <v>63</v>
@@ -29932,7 +29932,7 @@
     </row>
     <row r="674" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C674" s="2">
         <v>63</v>
@@ -29982,7 +29982,7 @@
     </row>
     <row r="675" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C675" s="2">
         <v>63</v>
@@ -30032,7 +30032,7 @@
     </row>
     <row r="676" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C676" s="2">
         <v>63</v>
@@ -30082,7 +30082,7 @@
     </row>
     <row r="677" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C677" s="2">
         <v>63</v>
@@ -30132,7 +30132,7 @@
     </row>
     <row r="678" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C678" s="2">
         <v>63</v>
@@ -30182,7 +30182,7 @@
     </row>
     <row r="679" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C679" s="2">
         <v>63</v>
@@ -30228,7 +30228,7 @@
     </row>
     <row r="680" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C680" s="2">
         <v>63</v>
@@ -30282,7 +30282,7 @@
     </row>
     <row r="681" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C681" s="2">
         <v>63</v>
@@ -30324,7 +30324,7 @@
     </row>
     <row r="682" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C682" s="2">
         <v>63</v>
@@ -30378,7 +30378,7 @@
     </row>
     <row r="683" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C683" s="2">
         <v>63</v>
@@ -30428,7 +30428,7 @@
     </row>
     <row r="684" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C684" s="2">
         <v>64</v>
@@ -30486,7 +30486,7 @@
     </row>
     <row r="685" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C685" s="2">
         <v>64</v>
@@ -30532,7 +30532,7 @@
     </row>
     <row r="686" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C686" s="2">
         <v>64</v>
@@ -30578,7 +30578,7 @@
     </row>
     <row r="687" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C687" s="2">
         <v>64</v>
@@ -30640,7 +30640,7 @@
     </row>
     <row r="688" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C688" s="2">
         <v>64</v>
@@ -30698,7 +30698,7 @@
     </row>
     <row r="689" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C689" s="2">
         <v>64</v>
@@ -30748,7 +30748,7 @@
     </row>
     <row r="690" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C690" s="2">
         <v>64</v>
@@ -30806,7 +30806,7 @@
     </row>
     <row r="691" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C691" s="2">
         <v>64</v>
@@ -30856,7 +30856,7 @@
     </row>
     <row r="692" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C692" s="2">
         <v>64</v>
@@ -30906,7 +30906,7 @@
     </row>
     <row r="693" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C693" s="2">
         <v>64</v>
@@ -30956,7 +30956,7 @@
     </row>
     <row r="694" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C694" s="2">
         <v>64</v>
@@ -31006,7 +31006,7 @@
     </row>
     <row r="695" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C695" s="2">
         <v>64</v>
@@ -31056,7 +31056,7 @@
     </row>
     <row r="696" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C696" s="2">
         <v>64</v>
@@ -31110,7 +31110,7 @@
     </row>
     <row r="697" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C697" s="2">
         <v>64</v>
@@ -31164,7 +31164,7 @@
     </row>
     <row r="698" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C698" s="2">
         <v>64</v>
@@ -31218,7 +31218,7 @@
     </row>
     <row r="699" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C699" s="2">
         <v>64</v>
@@ -31272,7 +31272,7 @@
     </row>
     <row r="700" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C700" s="2">
         <v>64</v>
@@ -31326,7 +31326,7 @@
     </row>
     <row r="701" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C701" s="2">
         <v>64</v>
@@ -31380,7 +31380,7 @@
     </row>
     <row r="702" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C702" s="2">
         <v>64</v>
@@ -31438,7 +31438,7 @@
     </row>
     <row r="703" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C703" s="2">
         <v>64</v>
@@ -31500,10 +31500,10 @@
     </row>
     <row r="704" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A704" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B704" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C704" s="5">
         <v>12</v>
@@ -31550,10 +31550,10 @@
     </row>
     <row r="705" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A705" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B705" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C705" s="5">
         <v>18</v>
@@ -31600,10 +31600,10 @@
     </row>
     <row r="706" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A706" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B706" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C706" s="5">
         <v>24</v>
@@ -31650,10 +31650,10 @@
     </row>
     <row r="707" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A707" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B707" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C707" s="4">
         <v>30</v>
@@ -31700,10 +31700,10 @@
     </row>
     <row r="708" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A708" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B708" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C708" s="4">
         <v>36</v>
@@ -31750,10 +31750,10 @@
     </row>
     <row r="709" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A709" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B709" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C709" s="4">
         <v>42</v>
@@ -31800,10 +31800,10 @@
     </row>
     <row r="710" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A710" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B710" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C710" s="4">
         <v>48</v>
@@ -31850,10 +31850,10 @@
     </row>
     <row r="711" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A711" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B711" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C711" s="4">
         <v>36</v>
@@ -31885,10 +31885,10 @@
     </row>
     <row r="712" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A712" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B712" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C712" s="4">
         <v>34</v>
@@ -31920,10 +31920,10 @@
     </row>
     <row r="713" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A713" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B713" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C713" s="4">
         <v>34</v>
@@ -31955,10 +31955,10 @@
     </row>
     <row r="714" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A714" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B714" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C714" s="4">
         <v>36</v>
@@ -31990,10 +31990,10 @@
     </row>
     <row r="715" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A715" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B715" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C715" s="4">
         <v>36</v>
@@ -32025,10 +32025,10 @@
     </row>
     <row r="716" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A716" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B716" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C716" s="4">
         <v>37</v>
@@ -32060,10 +32060,10 @@
     </row>
     <row r="717" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A717" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B717" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C717" s="4">
         <v>37</v>
@@ -32095,10 +32095,10 @@
     </row>
     <row r="718" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A718" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B718" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C718" s="4">
         <v>38</v>
@@ -32130,10 +32130,10 @@
     </row>
     <row r="719" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A719" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B719" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C719" s="4">
         <v>39</v>
@@ -32165,10 +32165,10 @@
     </row>
     <row r="720" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A720" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B720" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C720" s="4">
         <v>39</v>
@@ -32200,10 +32200,10 @@
     </row>
     <row r="721" spans="1:25" ht="29" x14ac:dyDescent="0.35">
       <c r="A721" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B721" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C721" s="4">
         <v>40</v>
@@ -32235,10 +32235,10 @@
     </row>
     <row r="722" spans="1:25" ht="29" x14ac:dyDescent="0.35">
       <c r="A722" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B722" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C722" s="4">
         <v>40</v>
@@ -32287,7 +32287,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -32298,13 +32298,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
         <v>45</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>46</v>
-      </c>
-      <c r="D2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -32911,7 +32911,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B46">
         <v>18</v>
@@ -32925,7 +32925,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B47">
         <v>27</v>
@@ -32939,7 +32939,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B48">
         <v>16</v>
@@ -32953,7 +32953,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B49">
         <v>21</v>
@@ -32967,7 +32967,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B50">
         <v>25</v>
@@ -32981,7 +32981,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B51">
         <v>30</v>
@@ -32995,7 +32995,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B52">
         <v>33</v>
@@ -33009,7 +33009,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B53">
         <v>14</v>
@@ -33023,7 +33023,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B54">
         <v>19</v>
@@ -33037,7 +33037,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B55">
         <v>24</v>
@@ -33051,7 +33051,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B56">
         <v>27</v>
@@ -33065,7 +33065,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B57">
         <v>30</v>
@@ -33079,7 +33079,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B58">
         <v>33</v>
@@ -33093,7 +33093,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B59">
         <v>23</v>
@@ -33107,7 +33107,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B60">
         <v>27</v>
@@ -33121,7 +33121,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B61">
         <v>31</v>
@@ -33135,7 +33135,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B62">
         <v>33</v>
@@ -33149,7 +33149,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B63">
         <v>34</v>
@@ -33163,7 +33163,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B64">
         <v>36</v>
@@ -33177,7 +33177,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B65">
         <v>21</v>
@@ -33191,7 +33191,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B66">
         <v>25</v>
@@ -33205,7 +33205,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B67">
         <v>28</v>
@@ -33219,7 +33219,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B68">
         <v>31</v>
@@ -33233,7 +33233,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B69">
         <v>33</v>
@@ -33247,7 +33247,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B70">
         <v>34</v>
@@ -33261,7 +33261,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B71">
         <v>36</v>
@@ -33275,7 +33275,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B72">
         <v>38</v>
@@ -33289,7 +33289,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B73">
         <v>39</v>
@@ -33303,7 +33303,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B74">
         <v>36</v>
@@ -33317,7 +33317,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B75">
         <v>30</v>
@@ -33331,7 +33331,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B76">
         <v>33</v>
@@ -33345,7 +33345,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B77">
         <v>36</v>
@@ -33359,7 +33359,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B78">
         <v>38</v>
@@ -33373,7 +33373,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B79">
         <v>40</v>
@@ -33387,7 +33387,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B80">
         <v>28</v>
@@ -33401,7 +33401,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B81">
         <v>33</v>
@@ -33415,7 +33415,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B82">
         <v>36</v>
@@ -33429,7 +33429,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B83">
         <v>38</v>
@@ -33443,7 +33443,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B84">
         <v>39</v>
@@ -33457,7 +33457,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B85" s="2">
         <v>18</v>
@@ -33471,7 +33471,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B86" s="2">
         <v>19</v>
@@ -33485,7 +33485,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B87" s="2">
         <v>21</v>
@@ -33499,7 +33499,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B88" s="2">
         <v>22</v>
@@ -33513,7 +33513,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B89" s="2">
         <v>23</v>
@@ -33527,7 +33527,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B90" s="2">
         <v>24</v>
@@ -33541,7 +33541,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B91" s="2">
         <v>25</v>
@@ -33555,7 +33555,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B92" s="2">
         <v>26</v>
@@ -33569,7 +33569,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B93" s="2">
         <v>27</v>
@@ -33583,7 +33583,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B94" s="2">
         <v>28</v>
@@ -33597,7 +33597,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B95" s="2">
         <v>29</v>
@@ -33611,7 +33611,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B96" s="2">
         <v>30</v>
@@ -33625,7 +33625,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B97" s="2">
         <v>31</v>
@@ -33639,7 +33639,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B98" s="2">
         <v>32</v>
@@ -33653,7 +33653,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B99" s="2">
         <v>33</v>
@@ -33667,7 +33667,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B100" s="2">
         <v>34</v>
@@ -33681,7 +33681,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B101" s="2">
         <v>35</v>
@@ -33695,7 +33695,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B102" s="2">
         <v>36</v>
@@ -33709,7 +33709,7 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B103" s="2">
         <v>37</v>
@@ -33723,7 +33723,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B104" s="2">
         <v>38</v>
@@ -33737,7 +33737,7 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B105" s="2">
         <v>39</v>
@@ -33751,7 +33751,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B106" s="2">
         <v>40</v>
@@ -33765,7 +33765,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B107" s="2">
         <v>41</v>
@@ -33779,7 +33779,7 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B108" s="2">
         <v>42</v>
@@ -33793,7 +33793,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B109" s="2">
         <v>43</v>
@@ -33807,7 +33807,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B110" s="2">
         <v>44</v>
@@ -33821,7 +33821,7 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B111" s="2">
         <v>45</v>
@@ -33835,7 +33835,7 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B112" s="2">
         <v>46</v>
@@ -33849,7 +33849,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B113" s="2">
         <v>47</v>
@@ -33863,7 +33863,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B114" s="2">
         <v>48</v>
@@ -33877,7 +33877,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B115" s="2">
         <v>18</v>
@@ -33891,7 +33891,7 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B116" s="2">
         <v>19</v>
@@ -33905,7 +33905,7 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B117" s="2">
         <v>21</v>
@@ -33919,7 +33919,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B118" s="2">
         <v>22</v>
@@ -33933,7 +33933,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B119" s="2">
         <v>23</v>
@@ -33947,7 +33947,7 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B120" s="2">
         <v>24</v>
@@ -33961,7 +33961,7 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B121" s="2">
         <v>25</v>
@@ -33975,7 +33975,7 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B122" s="2">
         <v>26</v>
@@ -33989,7 +33989,7 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B123" s="2">
         <v>27</v>
@@ -34003,7 +34003,7 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B124" s="2">
         <v>28</v>
@@ -34017,7 +34017,7 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B125" s="2">
         <v>29</v>
@@ -34031,7 +34031,7 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B126" s="2">
         <v>30</v>
@@ -34045,7 +34045,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B127" s="2">
         <v>31</v>
@@ -34059,7 +34059,7 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B128" s="2">
         <v>32</v>
@@ -34073,7 +34073,7 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B129" s="2">
         <v>33</v>
@@ -34087,7 +34087,7 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B130" s="2">
         <v>34</v>
@@ -34101,7 +34101,7 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B131" s="2">
         <v>35</v>
@@ -34115,7 +34115,7 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B132" s="2">
         <v>36</v>
@@ -34129,7 +34129,7 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B133" s="2">
         <v>37</v>
@@ -34143,7 +34143,7 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B134" s="2">
         <v>38</v>
@@ -34157,7 +34157,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B135" s="2">
         <v>39</v>
@@ -34171,7 +34171,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B136" s="2">
         <v>40</v>
@@ -34185,7 +34185,7 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B137" s="2">
         <v>41</v>
@@ -34199,7 +34199,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B138" s="2">
         <v>42</v>
@@ -34213,7 +34213,7 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B139" s="2">
         <v>43</v>
@@ -34227,7 +34227,7 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B140" s="2">
         <v>44</v>
@@ -34241,7 +34241,7 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B141" s="2">
         <v>45</v>
@@ -34255,7 +34255,7 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B142" s="2">
         <v>46</v>
@@ -34269,7 +34269,7 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B143" s="2">
         <v>47</v>
@@ -34283,7 +34283,7 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B144" s="2">
         <v>48</v>
@@ -34297,7 +34297,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B145" s="2">
         <v>49</v>
@@ -34311,7 +34311,7 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B146" s="2">
         <v>50</v>
@@ -34325,7 +34325,7 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B147" s="2">
         <v>51</v>
@@ -34339,7 +34339,7 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B148" s="2">
         <v>52</v>
@@ -34353,7 +34353,7 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B149" s="2">
         <v>53</v>
@@ -34367,7 +34367,7 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B150" s="2">
         <v>54</v>
@@ -34381,7 +34381,7 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B151" s="2">
         <v>55</v>
@@ -34395,7 +34395,7 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B152" s="2">
         <v>56</v>
@@ -34409,7 +34409,7 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B153" s="2">
         <v>18</v>
@@ -34423,7 +34423,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B154" s="2">
         <v>19</v>
@@ -34437,7 +34437,7 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B155" s="2">
         <v>21</v>
@@ -34451,7 +34451,7 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B156" s="2">
         <v>22</v>
@@ -34465,7 +34465,7 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B157" s="2">
         <v>24</v>
@@ -34479,7 +34479,7 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B158" s="2">
         <v>25</v>
@@ -34493,7 +34493,7 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B159" s="2">
         <v>27</v>
@@ -34507,7 +34507,7 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B160" s="2">
         <v>28</v>
@@ -34521,7 +34521,7 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B161" s="2">
         <v>30</v>
@@ -34535,7 +34535,7 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B162" s="2">
         <v>31</v>
@@ -34549,7 +34549,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B163" s="2">
         <v>33</v>
@@ -34563,7 +34563,7 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B164" s="2">
         <v>34</v>
@@ -34577,7 +34577,7 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B165" s="2">
         <v>36</v>
@@ -34591,7 +34591,7 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B166" s="2">
         <v>37</v>
@@ -34605,7 +34605,7 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B167" s="2">
         <v>39</v>
@@ -34619,7 +34619,7 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B168" s="2">
         <v>40</v>
@@ -34633,7 +34633,7 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B169" s="2">
         <v>42</v>
@@ -34647,7 +34647,7 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B170" s="2">
         <v>43</v>
@@ -34661,7 +34661,7 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B171" s="2">
         <v>45</v>
@@ -34675,7 +34675,7 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B172" s="2">
         <v>46</v>
@@ -34689,7 +34689,7 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B173" s="2">
         <v>48</v>
@@ -34703,7 +34703,7 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B174" s="2">
         <v>49</v>
@@ -34717,7 +34717,7 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B175" s="2">
         <v>51</v>
@@ -34731,7 +34731,7 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B176" s="2">
         <v>52</v>
@@ -34745,7 +34745,7 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B177" s="2">
         <v>54</v>
@@ -34759,7 +34759,7 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B178" s="2">
         <v>55</v>
@@ -34773,7 +34773,7 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B179" s="2">
         <v>57</v>
@@ -34787,7 +34787,7 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B180" s="2">
         <v>58</v>
@@ -34801,7 +34801,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B181" s="2">
         <v>60</v>
@@ -34815,7 +34815,7 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B182" s="2">
         <v>61</v>
@@ -34829,7 +34829,7 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B183" s="2">
         <v>63</v>
@@ -34843,7 +34843,7 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B184" s="2">
         <v>64</v>
